--- a/data/warn-scraper/cache/ri/WARN Report.xlsx
+++ b/data/warn-scraper/cache/ri/WARN Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nathaniel.m.wilson\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5360400D-715B-4154-8942-33DFE93F2C3A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="201">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -71,6 +71,27 @@
     <t>Union Address</t>
   </si>
   <si>
+    <t>Northeast Transportation Services LLC</t>
+  </si>
+  <si>
+    <t>Pawtucket, RI</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
+  </si>
+  <si>
+    <t>EaglePicher</t>
+  </si>
+  <si>
+    <t>East Greenwich</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>UNFI</t>
   </si>
   <si>
@@ -98,9 +119,6 @@
     <t>Lincoln</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>CVS</t>
   </si>
   <si>
@@ -197,15 +215,9 @@
     <t>UPS</t>
   </si>
   <si>
-    <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
-  </si>
-  <si>
     <t>Los Angeles Times Communications LLC</t>
   </si>
   <si>
-    <t>East Greenwich, RI</t>
-  </si>
-  <si>
     <t>Company Name (* Denotes Covid 19 Related WARN)</t>
   </si>
   <si>
@@ -251,9 +263,6 @@
     <t>Local Union 1033, 410 S Main Street 3rd floor, Providence, RI 02906</t>
   </si>
   <si>
-    <t>Northeast Transportation Services LLC</t>
-  </si>
-  <si>
     <t>Teamster Local Union 251 121 Brightridge Ave. East Providence, RI 02914</t>
   </si>
   <si>
@@ -566,9 +575,6 @@
     <t>Stanley Black &amp; Decker</t>
   </si>
   <si>
-    <t>East Greenwich</t>
-  </si>
-  <si>
     <t>Wal-Mart Stores, Inc. /Sam’s Club</t>
   </si>
   <si>
@@ -636,9 +642,6 @@
   </si>
   <si>
     <t>East Providence and Providence</t>
-  </si>
-  <si>
-    <t>EaglePicher</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -971,15 +974,41 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,9 +1028,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1039,7 +1068,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1145,7 +1174,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1287,7 +1316,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1295,44 +1324,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="13.09765625" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="18.3984375" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" customWidth="1"/>
-    <col min="5" max="5" width="16.19921875" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" customWidth="1"/>
-    <col min="7" max="7" width="20.19921875" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="51.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.2">
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3" s="76"/>
       <c r="B3" s="76"/>
       <c r="C3" s="52"/>
@@ -1343,32 +1373,32 @@
       <c r="H3" s="76"/>
       <c r="I3" s="76"/>
     </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A4" s="70" t="s">
+    <row r="4" spans="1:19" s="59" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A4" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="82" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1382,27 +1412,69 @@
       <c r="R4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="77">
+    <row r="5" spans="1:19" s="81" customFormat="1" ht="32.25">
+      <c r="A5" s="78">
+        <v>46100</v>
+      </c>
+      <c r="B5" s="78">
+        <v>46100</v>
+      </c>
+      <c r="C5" s="79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="86">
+        <v>52</v>
+      </c>
+      <c r="F5" s="78">
+        <v>46151</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="75">
         <v>46035</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B6" s="75">
         <v>46035</v>
       </c>
-      <c r="C5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5">
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="28">
         <v>38</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F6" s="75">
         <v>46096</v>
       </c>
-      <c r="G5" t="s">
-        <v>19</v>
+      <c r="G6" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1419,55 +1491,55 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19.8" customHeight="1">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-    </row>
-    <row r="2" spans="1:19" ht="19.8" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-    </row>
-    <row r="3" spans="1:19" ht="19.8" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+    </row>
+    <row r="2" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="52"/>
-      <c r="D3" s="75"/>
+      <c r="D3" s="76"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-    </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.8" customHeight="1">
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+    </row>
+    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A4" s="70" t="s">
         <v>1</v>
       </c>
@@ -1514,10 +1586,10 @@
         <v>45910</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="67">
         <v>2</v>
@@ -1526,10 +1598,10 @@
         <v>45975</v>
       </c>
       <c r="G5" s="68" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H5" s="68" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="68"/>
       <c r="J5"/>
@@ -1551,10 +1623,10 @@
         <v>45903</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E6" s="67">
         <v>105</v>
@@ -1563,13 +1635,13 @@
         <v>45964</v>
       </c>
       <c r="G6" s="66" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H6" s="66" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I6" s="66" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -1582,7 +1654,7 @@
       <c r="R6"/>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" s="59" customFormat="1" ht="31.2">
+    <row r="7" spans="1:19" s="59" customFormat="1" ht="31.5">
       <c r="A7" s="68">
         <v>45814</v>
       </c>
@@ -1590,10 +1662,10 @@
         <v>45816</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E7" s="67">
         <v>125</v>
@@ -1602,10 +1674,10 @@
         <v>45874</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H7" s="66" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1627,10 +1699,10 @@
         <v>45736</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E8" s="67">
         <v>20</v>
@@ -1639,10 +1711,10 @@
         <v>45800</v>
       </c>
       <c r="G8" s="66" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H8" s="66" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1664,20 +1736,20 @@
         <v>45694</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E9" s="68"/>
       <c r="F9" s="68">
         <v>45815</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1705,55 +1777,55 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S123"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="49.5" style="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.3984375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="28.3984375" style="51" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="28.375" style="51" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.59765625" customWidth="1"/>
+    <col min="9" max="9" width="71.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.2">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.5">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="52"/>
-      <c r="D3" s="75"/>
+      <c r="D3" s="76"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-    </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.8" customHeight="1">
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+    </row>
+    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A4" s="70" t="s">
         <v>1</v>
       </c>
@@ -1800,10 +1872,10 @@
         <v>45621</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5" s="38">
         <v>796</v>
@@ -1812,10 +1884,10 @@
         <v>45682</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="38"/>
     </row>
@@ -1827,10 +1899,10 @@
         <v>45617</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E6" s="38">
         <v>121</v>
@@ -1839,10 +1911,10 @@
         <v>45681</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="34"/>
@@ -1864,10 +1936,10 @@
         <v>45608</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E7" s="38">
         <v>136</v>
@@ -1876,13 +1948,13 @@
         <v>45726</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
@@ -1903,22 +1975,22 @@
         <v>45572</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E8" s="38">
         <v>632</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
@@ -1940,10 +2012,10 @@
         <v>45567</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E9" s="38">
         <v>1</v>
@@ -1952,7 +2024,7 @@
         <v>45626</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
@@ -1965,20 +2037,20 @@
         <v>45560</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E10" s="38">
         <v>13</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I10" s="38"/>
     </row>
@@ -1990,20 +2062,20 @@
         <v>45526</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" s="38">
         <v>117</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I11" s="38"/>
     </row>
@@ -2015,10 +2087,10 @@
         <v>45504</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E12" s="38">
         <v>205</v>
@@ -2027,10 +2099,10 @@
         <v>45658</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I12" s="38"/>
     </row>
@@ -2042,10 +2114,10 @@
         <v>45485</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E13" s="38">
         <v>58</v>
@@ -2054,10 +2126,10 @@
         <v>45541</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I13" s="38"/>
     </row>
@@ -2069,10 +2141,10 @@
         <v>45432</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E14" s="38">
         <v>30</v>
@@ -2081,27 +2153,27 @@
         <v>45488</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B15" s="40">
         <v>45421</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E15" s="38">
         <v>1029</v>
@@ -2110,13 +2182,13 @@
         <v>45473</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2127,22 +2199,22 @@
         <v>45414</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E16" s="38">
         <v>36</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I16" s="38"/>
     </row>
@@ -2154,22 +2226,22 @@
         <v>45383</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F17" s="40">
         <v>45412</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I17" s="38"/>
     </row>
@@ -2181,10 +2253,10 @@
         <v>45383</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E18" s="38">
         <v>1</v>
@@ -2193,10 +2265,10 @@
         <v>45443</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I18" s="38"/>
     </row>
@@ -2208,10 +2280,10 @@
         <v>45349</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E19" s="38">
         <v>48</v>
@@ -2220,10 +2292,10 @@
         <v>45611</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I19" s="38"/>
     </row>
@@ -2235,10 +2307,10 @@
         <v>45328</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E20" s="38">
         <v>130</v>
@@ -2247,13 +2319,13 @@
         <v>45384</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2264,10 +2336,10 @@
         <v>45316</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E21" s="38">
         <v>1</v>
@@ -2276,10 +2348,10 @@
         <v>45316</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I21" s="40"/>
     </row>
@@ -3316,53 +3388,53 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="103.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="103.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-    </row>
-    <row r="3" spans="1:9" ht="31.2">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+    </row>
+    <row r="3" spans="1:9" ht="31.5">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1">
       <c r="A4" s="35" t="s">
@@ -3372,7 +3444,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>4</v>
@@ -3393,7 +3465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A5" s="60">
         <v>45191</v>
       </c>
@@ -3401,10 +3473,10 @@
         <v>45191</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6">
         <v>136</v>
@@ -3413,14 +3485,14 @@
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A6" s="60">
         <v>45156</v>
       </c>
@@ -3428,26 +3500,26 @@
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A7" s="60">
         <v>45191</v>
       </c>
@@ -3455,10 +3527,10 @@
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E7" s="38">
         <v>52</v>
@@ -3467,13 +3539,13 @@
         <v>45153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A8" s="60">
         <v>45156</v>
       </c>
@@ -3481,10 +3553,10 @@
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E8" s="6">
         <v>211</v>
@@ -3493,16 +3565,16 @@
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A9" s="40">
         <v>45153</v>
       </c>
@@ -3510,10 +3582,10 @@
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" s="6">
         <v>249</v>
@@ -3522,16 +3594,16 @@
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A10" s="60">
         <v>45112</v>
       </c>
@@ -3539,10 +3611,10 @@
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E10" s="6">
         <v>169</v>
@@ -3551,16 +3623,16 @@
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A11" s="60">
         <v>45107</v>
       </c>
@@ -3568,10 +3640,10 @@
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" s="6">
         <v>75</v>
@@ -3580,16 +3652,16 @@
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A12" s="60">
         <v>45063</v>
       </c>
@@ -3597,10 +3669,10 @@
         <v>44937</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E12" s="38">
         <v>81</v>
@@ -3609,14 +3681,14 @@
         <v>44990</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A13" s="62">
         <v>44949</v>
       </c>
@@ -3624,10 +3696,10 @@
         <v>44831</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E13" s="63">
         <v>1</v>
@@ -3636,14 +3708,14 @@
         <v>44890</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A14" s="40">
         <v>44930</v>
       </c>
@@ -3651,10 +3723,10 @@
         <v>44817</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E14" s="63">
         <v>77</v>
@@ -3663,14 +3735,14 @@
         <v>44880</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A15" s="22">
         <v>44827</v>
       </c>
@@ -3678,10 +3750,10 @@
         <v>44594</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E15" s="64">
         <v>198</v>
@@ -3690,13 +3762,13 @@
         <v>44659</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A16" s="22">
         <v>44817</v>
       </c>
@@ -3704,10 +3776,10 @@
         <v>44336</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E16" s="64">
         <v>94</v>
@@ -3716,16 +3788,16 @@
         <v>44394</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A17" s="22">
         <v>44595</v>
       </c>
@@ -3733,10 +3805,10 @@
         <v>44342</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E17" s="64">
         <v>464</v>
@@ -3745,13 +3817,13 @@
         <v>44403</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A18" s="22">
         <v>44334</v>
       </c>
@@ -3759,10 +3831,10 @@
         <v>44104</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E18" s="64">
         <v>13</v>
@@ -3771,13 +3843,13 @@
         <v>44104</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A19" s="22">
         <v>44342</v>
       </c>
@@ -3785,10 +3857,10 @@
         <v>44068</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E19" s="64">
         <v>40</v>
@@ -3797,13 +3869,13 @@
         <v>44061</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A20" s="22">
         <v>44105</v>
       </c>
@@ -3811,10 +3883,10 @@
         <v>44060</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E20" s="64">
         <v>106</v>
@@ -3823,13 +3895,13 @@
         <v>44057</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A21" s="22">
         <v>44064</v>
       </c>
@@ -3837,10 +3909,10 @@
         <v>44056</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E21" s="64">
         <v>272</v>
@@ -3849,16 +3921,16 @@
         <v>43914</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A22" s="22">
         <v>44057</v>
       </c>
@@ -3866,10 +3938,10 @@
         <v>44040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E22" s="64">
         <v>1043</v>
@@ -3878,16 +3950,16 @@
         <v>44104</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A23" s="22">
         <v>44049</v>
       </c>
@@ -3895,10 +3967,10 @@
         <v>44040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E23" s="64">
         <v>296</v>
@@ -3907,16 +3979,16 @@
         <v>44104</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A24" s="22">
         <v>44054</v>
       </c>
@@ -3924,10 +3996,10 @@
         <v>44042</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E24" s="64">
         <v>73</v>
@@ -3936,13 +4008,13 @@
         <v>44075</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A25" s="22">
         <v>44054</v>
       </c>
@@ -3950,10 +4022,10 @@
         <v>44022</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E25" s="64">
         <v>127</v>
@@ -3962,16 +4034,16 @@
         <v>44044</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A26" s="22">
         <v>44046</v>
       </c>
@@ -3979,10 +4051,10 @@
         <v>44004</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E26" s="64">
         <v>71</v>
@@ -3991,13 +4063,13 @@
         <v>43973</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A27" s="22">
         <v>44027</v>
       </c>
@@ -4005,10 +4077,10 @@
         <v>44012</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E27" s="64">
         <v>65</v>
@@ -4017,13 +4089,13 @@
         <v>44012</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A28" s="22">
         <v>44004</v>
       </c>
@@ -4031,10 +4103,10 @@
         <v>43985</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E28" s="64">
         <v>65</v>
@@ -4043,13 +4115,13 @@
         <v>43904</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A29" s="22">
         <v>44012</v>
       </c>
@@ -4057,10 +4129,10 @@
         <v>43980</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E29" s="64">
         <v>231</v>
@@ -4069,13 +4141,13 @@
         <v>43980</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A30" s="22">
         <v>43985</v>
       </c>
@@ -4083,10 +4155,10 @@
         <v>44068</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E30" s="64">
         <v>72</v>
@@ -4095,13 +4167,13 @@
         <v>43958</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A31" s="22">
         <v>43980</v>
       </c>
@@ -4109,10 +4181,10 @@
         <v>43948</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E31" s="64">
         <v>136</v>
@@ -4121,13 +4193,13 @@
         <v>43906</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A32" s="40">
         <v>44063</v>
       </c>
@@ -4135,10 +4207,10 @@
         <v>43942</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E32" s="64">
         <v>5</v>
@@ -4147,13 +4219,13 @@
         <v>43942</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A33" s="40">
         <v>43948</v>
       </c>
@@ -4161,10 +4233,10 @@
         <v>43944</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E33" s="64">
         <v>1</v>
@@ -4173,13 +4245,13 @@
         <v>43941</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A34" s="40">
         <v>43942</v>
       </c>
@@ -4187,10 +4259,10 @@
         <v>43938</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E34" s="64">
         <v>13</v>
@@ -4199,13 +4271,13 @@
         <v>43938</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A35" s="22">
         <v>43941</v>
       </c>
@@ -4213,10 +4285,10 @@
         <v>43935</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E35" s="64">
         <v>51</v>
@@ -4225,13 +4297,13 @@
         <v>43906</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A36" s="22">
         <v>43907</v>
       </c>
@@ -4239,10 +4311,10 @@
         <v>43925</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E36" s="64">
         <v>110</v>
@@ -4251,13 +4323,13 @@
         <v>43927</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A37" s="22">
         <v>43927</v>
       </c>
@@ -4265,10 +4337,10 @@
         <v>43917</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E37" s="64">
         <v>37</v>
@@ -4277,13 +4349,13 @@
         <v>43916</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A38" s="22">
         <v>43925</v>
       </c>
@@ -4291,10 +4363,10 @@
         <v>43913</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E38" s="64">
         <v>146</v>
@@ -4303,16 +4375,16 @@
         <v>43898</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A39" s="22">
         <v>43916</v>
       </c>
@@ -4320,10 +4392,10 @@
         <v>43910</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E39" s="64">
         <v>87</v>
@@ -4332,13 +4404,13 @@
         <v>43910</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A40" s="22">
         <v>43916</v>
       </c>
@@ -4346,10 +4418,10 @@
         <v>43913</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E40" s="64">
         <v>110</v>
@@ -4358,13 +4430,13 @@
         <v>43906</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A41" s="22">
         <v>43910</v>
       </c>
@@ -4372,10 +4444,10 @@
         <v>43510</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E41" s="64">
         <v>1</v>
@@ -4384,13 +4456,13 @@
         <v>43567</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A42" s="22">
         <v>43909</v>
       </c>
@@ -4398,25 +4470,25 @@
         <v>43486</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E42" s="64">
         <v>59</v>
       </c>
       <c r="F42" s="64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A43" s="22">
         <v>43509</v>
       </c>
@@ -4424,10 +4496,10 @@
         <v>43479</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E43" s="64">
         <v>62</v>
@@ -4436,13 +4508,13 @@
         <v>43542</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A44" s="22">
         <v>43486</v>
       </c>
@@ -4450,10 +4522,10 @@
         <v>43413</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E44" s="64">
         <v>51</v>
@@ -4462,13 +4534,13 @@
         <v>43131</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A45" s="22">
         <v>43479</v>
       </c>
@@ -4476,10 +4548,10 @@
         <v>43405</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E45" s="64">
         <v>92</v>
@@ -4488,13 +4560,13 @@
         <v>43465</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A46" s="22">
         <v>43405</v>
       </c>
@@ -4502,10 +4574,10 @@
         <v>43405</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E46" s="64">
         <v>181</v>
@@ -4514,13 +4586,13 @@
         <v>43469</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A47" s="22">
         <v>76277</v>
       </c>
@@ -4528,10 +4600,10 @@
         <v>43382</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E47" s="64">
         <v>180</v>
@@ -4540,13 +4612,13 @@
         <v>43382</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A48" s="22">
         <v>76268</v>
       </c>
@@ -4554,10 +4626,10 @@
         <v>43363</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E48" s="64">
         <v>83</v>
@@ -4566,13 +4638,13 @@
         <v>43434</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A49" s="22">
         <v>43382</v>
       </c>
@@ -4580,10 +4652,10 @@
         <v>43276</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E49" s="64">
         <v>64</v>
@@ -4592,16 +4664,16 @@
         <v>43339</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A50" s="22">
         <v>43362</v>
       </c>
@@ -4609,10 +4681,10 @@
         <v>43252</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E50" s="64">
         <v>149</v>
@@ -4621,13 +4693,13 @@
         <v>43312</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A51" s="22">
         <v>43273</v>
       </c>
@@ -4635,10 +4707,10 @@
         <v>43042</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E51" s="64">
         <v>477</v>
@@ -4647,16 +4719,16 @@
         <v>43112</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A52" s="22">
         <v>43252</v>
       </c>
@@ -4664,25 +4736,25 @@
         <v>42990</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E52" s="64">
         <v>171</v>
       </c>
       <c r="F52" s="64" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A53" s="22">
         <v>43042</v>
       </c>
@@ -4690,10 +4762,10 @@
         <v>42496</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E53" s="64">
         <v>187</v>
@@ -4702,13 +4774,13 @@
         <v>42492</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A54" s="22">
         <v>42986</v>
       </c>
@@ -4716,10 +4788,10 @@
         <v>42495</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E54" s="64">
         <v>20</v>
@@ -4728,16 +4800,16 @@
         <v>42551</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A55" s="22">
         <v>42495</v>
       </c>
@@ -4745,10 +4817,10 @@
         <v>42468</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E55" s="64">
         <v>154</v>
@@ -4757,13 +4829,13 @@
         <v>42528</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A56" s="22">
         <v>42494</v>
       </c>
@@ -4771,25 +4843,25 @@
         <v>42401</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E56" s="64">
         <v>60</v>
       </c>
       <c r="F56" s="64" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A57" s="22">
         <v>42468</v>
       </c>
@@ -4797,10 +4869,10 @@
         <v>42384</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E57" s="64">
         <v>131</v>
@@ -4809,13 +4881,13 @@
         <v>42405</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A58" s="22">
         <v>42401</v>
       </c>
@@ -4823,25 +4895,25 @@
         <v>42326</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E58" s="64">
         <v>241</v>
       </c>
       <c r="F58" s="64" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A59" s="22">
         <v>42384</v>
       </c>
@@ -4849,25 +4921,25 @@
         <v>42320</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E59" s="64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F59" s="64" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A60" s="22">
         <v>42326</v>
       </c>
@@ -4875,10 +4947,10 @@
         <v>42180</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E60" s="64">
         <v>70</v>
@@ -4887,13 +4959,13 @@
         <v>42240</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A61" s="22">
         <v>42318</v>
       </c>
@@ -4901,28 +4973,28 @@
         <v>42074</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E61" s="64" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F61" s="22">
         <v>42141</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A62" s="22">
         <v>42178</v>
       </c>
@@ -4930,25 +5002,25 @@
         <v>42065</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E62" s="64" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F62" s="64" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A63" s="22">
         <v>42069</v>
       </c>
@@ -4956,10 +5028,10 @@
         <v>41850</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E63" s="64">
         <v>5</v>
@@ -4968,13 +5040,13 @@
         <v>41912</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A64" s="22">
         <v>42062</v>
       </c>
@@ -4982,10 +5054,10 @@
         <v>41821</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E64" s="64">
         <v>142</v>
@@ -4994,13 +5066,13 @@
         <v>41882</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A65" s="22">
         <v>41850</v>
       </c>
@@ -5008,10 +5080,10 @@
         <v>41729</v>
       </c>
       <c r="C65" s="24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E65" s="64">
         <v>115</v>
@@ -5020,16 +5092,16 @@
         <v>41774</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A66" s="22">
         <v>41820</v>
       </c>
@@ -5037,10 +5109,10 @@
         <v>41596</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E66" s="64">
         <v>49</v>
@@ -5049,13 +5121,13 @@
         <v>41654</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A67" s="22">
         <v>41724</v>
       </c>
@@ -5063,10 +5135,10 @@
         <v>41547</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E67" s="64">
         <v>1</v>
@@ -5075,13 +5147,13 @@
         <v>41608</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A68" s="22">
         <v>41593</v>
       </c>
@@ -5089,10 +5161,10 @@
         <v>41502</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E68" s="64">
         <v>66</v>
@@ -5101,13 +5173,13 @@
         <v>41555</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A69" s="22">
         <v>41547</v>
       </c>
@@ -5115,10 +5187,10 @@
         <v>41438</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E69" s="64">
         <v>3</v>
@@ -5127,13 +5199,13 @@
         <v>41425</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A70" s="22">
         <v>41495</v>
       </c>
@@ -5141,10 +5213,10 @@
         <v>41417</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E70" s="64">
         <v>62</v>
@@ -5153,13 +5225,13 @@
         <v>41485</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A71" s="22">
         <v>41425</v>
       </c>
@@ -5167,25 +5239,25 @@
         <v>41285</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E71" s="64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F71" s="22">
         <v>41347</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A72" s="22">
         <v>41416</v>
       </c>
@@ -5193,10 +5265,10 @@
         <v>41087</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E72" s="64">
         <v>51</v>
@@ -5205,13 +5277,13 @@
         <v>41148</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A73" s="22">
         <v>41285</v>
       </c>
@@ -5219,10 +5291,10 @@
         <v>41011</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E73" s="64">
         <v>150</v>
@@ -5231,16 +5303,16 @@
         <v>41071</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A74" s="22">
         <v>41087</v>
       </c>
@@ -5248,10 +5320,10 @@
         <v>40939</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E74" s="64">
         <v>70</v>
@@ -5260,16 +5332,16 @@
         <v>41000</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A75" s="22">
         <v>41011</v>
       </c>
@@ -5277,10 +5349,10 @@
         <v>40833</v>
       </c>
       <c r="C75" s="24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E75" s="64">
         <v>110</v>
@@ -5289,14 +5361,14 @@
         <v>40833</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I75" s="24"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A76" s="22">
         <v>40938</v>
       </c>
@@ -5304,10 +5376,10 @@
         <v>40788</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E76" s="64">
         <v>16</v>
@@ -5316,14 +5388,14 @@
         <v>40846</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I76" s="24"/>
     </row>
-    <row r="77" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="77" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A77" s="22">
         <v>40833</v>
       </c>
@@ -5331,10 +5403,10 @@
         <v>40758</v>
       </c>
       <c r="C77" s="24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E77" s="64">
         <v>9</v>
@@ -5343,14 +5415,14 @@
         <v>40816</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I77" s="24"/>
     </row>
-    <row r="78" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="78" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A78" s="22">
         <v>40785</v>
       </c>
@@ -5358,26 +5430,26 @@
         <v>40756</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E78" s="64">
         <v>98</v>
       </c>
       <c r="F78" s="64" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I78" s="24"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A79" s="22">
         <v>40752</v>
       </c>
@@ -5385,26 +5457,26 @@
         <v>40690</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E79" s="64">
         <v>21</v>
       </c>
       <c r="F79" s="64" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I79" s="24"/>
     </row>
-    <row r="80" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="80" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A80" s="22">
         <v>40753</v>
       </c>
@@ -5412,26 +5484,26 @@
         <v>40634</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E80" s="64">
         <v>98</v>
       </c>
       <c r="F80" s="64" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I80" s="24"/>
     </row>
-    <row r="81" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="81" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A81" s="22">
         <v>40688</v>
       </c>
@@ -5439,10 +5511,10 @@
         <v>40589</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="E81" s="64">
         <v>5</v>
@@ -5451,14 +5523,14 @@
         <v>40644</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I81" s="24"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A82" s="22">
         <v>40634</v>
       </c>
@@ -5466,10 +5538,10 @@
         <v>40568</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E82" s="64">
         <v>122</v>
@@ -5478,14 +5550,14 @@
         <v>40592</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I82" s="24"/>
     </row>
-    <row r="83" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="83" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A83" s="22">
         <v>40589</v>
       </c>
@@ -5493,10 +5565,10 @@
         <v>40413</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E83" s="64">
         <v>89</v>
@@ -5505,14 +5577,14 @@
         <v>40452</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I83" s="24"/>
     </row>
-    <row r="84" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="84" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A84" s="22">
         <v>40565</v>
       </c>
@@ -5520,26 +5592,26 @@
         <v>40217</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D84" s="24" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="E84" s="64">
         <v>26</v>
       </c>
       <c r="F84" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I84" s="24"/>
     </row>
-    <row r="85" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="85" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A85" s="22">
         <v>40410</v>
       </c>
@@ -5547,10 +5619,10 @@
         <v>40217</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="E85" s="64">
         <v>165</v>
@@ -5559,14 +5631,14 @@
         <v>40217</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I85" s="24"/>
     </row>
-    <row r="86" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="86" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A86" s="22">
         <v>40392</v>
       </c>
@@ -5574,10 +5646,10 @@
         <v>40182</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E86" s="64">
         <v>8</v>
@@ -5586,14 +5658,14 @@
         <v>40210</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A87" s="22">
         <v>40214</v>
       </c>
@@ -5601,26 +5673,26 @@
         <v>40141</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E87" s="64">
         <v>66</v>
       </c>
       <c r="F87" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I87" s="24"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A88" s="22">
         <v>40178</v>
       </c>
@@ -5628,28 +5700,28 @@
         <v>40141</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E88" s="64">
         <v>103</v>
       </c>
       <c r="F88" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A89" s="22">
         <v>40137</v>
       </c>
@@ -5657,25 +5729,25 @@
         <v>40094</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E89" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F89" s="22">
         <v>40147</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A90" s="22">
         <v>40137</v>
       </c>
@@ -5683,10 +5755,10 @@
         <v>40091</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E90" s="64">
         <v>63</v>
@@ -5695,13 +5767,13 @@
         <v>40148</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A91" s="22">
         <v>40094</v>
       </c>
@@ -5709,25 +5781,25 @@
         <v>40050</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E91" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F91" s="22">
         <v>39895</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A92" s="22">
         <v>40091</v>
       </c>
@@ -5735,10 +5807,10 @@
         <v>40008</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E92" s="64">
         <v>130</v>
@@ -5747,13 +5819,13 @@
         <v>39895</v>
       </c>
       <c r="G92" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A93" s="22">
         <v>40046</v>
       </c>
@@ -5761,10 +5833,10 @@
         <v>40008</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E93" s="64">
         <v>26</v>
@@ -5773,13 +5845,13 @@
         <v>40001</v>
       </c>
       <c r="G93" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A94" s="22">
         <v>40007</v>
       </c>
@@ -5787,10 +5859,10 @@
         <v>39895</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E94" s="64">
         <v>14</v>
@@ -5799,13 +5871,13 @@
         <v>39895</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A95" s="22">
         <v>40007</v>
       </c>
@@ -5813,10 +5885,10 @@
         <v>39996</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E95" s="64">
         <v>10</v>
@@ -5825,13 +5897,13 @@
         <v>40041</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="14.25">
       <c r="A96" s="22">
         <v>39995</v>
       </c>
@@ -5839,10 +5911,10 @@
         <v>39932</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E96" s="64">
         <v>171</v>
@@ -5851,16 +5923,16 @@
         <v>39994</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A97" s="22">
         <v>39980</v>
       </c>
@@ -5868,10 +5940,10 @@
         <v>39918</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E97" s="64">
         <v>55</v>
@@ -5880,13 +5952,13 @@
         <v>39994</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A98" s="22">
         <v>39931</v>
       </c>
@@ -5894,10 +5966,10 @@
         <v>39882</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E98" s="64">
         <v>29</v>
@@ -5906,13 +5978,13 @@
         <v>39943</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A99" s="22">
         <v>39918</v>
       </c>
@@ -5920,10 +5992,10 @@
         <v>39881</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E99" s="64">
         <v>71</v>
@@ -5932,13 +6004,13 @@
         <v>39941</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A100" s="22">
         <v>39883</v>
       </c>
@@ -5946,10 +6018,10 @@
         <v>39878</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D100" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E100" s="64">
         <v>54</v>
@@ -5958,13 +6030,13 @@
         <v>39935</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A101" s="22">
         <v>39881</v>
       </c>
@@ -5972,10 +6044,10 @@
         <v>39877</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D101" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E101" s="64">
         <v>119</v>
@@ -5984,13 +6056,13 @@
         <v>39943</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A102" s="22">
         <v>39876</v>
       </c>
@@ -5998,10 +6070,10 @@
         <v>39864</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D102" s="24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E102" s="64">
         <v>270</v>
@@ -6010,13 +6082,13 @@
         <v>39828</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="5" customFormat="1" ht="14.25">
       <c r="A103" s="22">
         <v>39877</v>
       </c>
@@ -6024,10 +6096,10 @@
         <v>39825</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D103" s="24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E103" s="64">
         <v>121</v>
@@ -6036,10 +6108,10 @@
         <v>39821</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -7215,17 +7287,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D7CA4A7758DDF4F8A78677D3B22BD47" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40fb347cb6748129dfb5d7e3644aefd9">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e19eab3b-0a92-46fc-9552-a493c76cdc00" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7d33a88d0aab069d8ee7b3bf8b77c32a" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D7CA4A7758DDF4F8A78677D3B22BD47" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f32e13009e9660c0d5c2c5b7ed8445ba">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e19eab3b-0a92-46fc-9552-a493c76cdc00" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dceef0fefb3dead4f6c07070271e1f3" ns2:_="">
     <xsd:import namespace="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -7367,37 +7430,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B637F5-46E4-4C64-84F3-43D9F3F75167}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
 </file>
--- a/data/warn-scraper/cache/ri/WARN Report.xlsx
+++ b/data/warn-scraper/cache/ri/WARN Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5360400D-715B-4154-8942-33DFE93F2C3A}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75CB4929-1866-446D-A065-3EE9F4FF02C9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="203">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -71,15 +71,27 @@
     <t>Union Address</t>
   </si>
   <si>
+    <t>Allied Group, LLC</t>
+  </si>
+  <si>
+    <t>Cumberland, RI</t>
+  </si>
+  <si>
+    <t>5/25/26 - 6/6/26</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Northeast Transportation Services LLC</t>
   </si>
   <si>
     <t>Pawtucket, RI</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
   </si>
   <si>
@@ -89,16 +101,10 @@
     <t>East Greenwich</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>UNFI</t>
   </si>
   <si>
     <t>Lincon</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Hotel Viking</t>
@@ -980,9 +986,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1009,6 +1012,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -1339,28 +1345,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
     </row>
     <row r="3" spans="1:19" ht="31.5">
       <c r="A3" s="76"/>
@@ -1374,31 +1380,31 @@
       <c r="I3" s="76"/>
     </row>
     <row r="4" spans="1:19" s="59" customFormat="1" ht="22.15" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="83" t="s">
+      <c r="F4" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="85" t="s">
+      <c r="G4" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="82" t="s">
+      <c r="H4" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="82" t="s">
+      <c r="I4" s="81" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1412,69 +1418,106 @@
       <c r="R4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="1:19" s="81" customFormat="1" ht="32.25">
-      <c r="A5" s="78">
+    <row r="5" spans="1:19" s="59" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A5" s="77">
+        <v>46107</v>
+      </c>
+      <c r="B5" s="77">
+        <v>46112</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="85">
+        <v>154</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="78"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+    </row>
+    <row r="6" spans="1:19" s="80" customFormat="1" ht="32.25">
+      <c r="A6" s="77">
         <v>46100</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B6" s="77">
         <v>46100</v>
       </c>
-      <c r="C5" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="80" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="86">
+      <c r="C6" s="78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="85">
         <v>52</v>
       </c>
-      <c r="F5" s="78">
+      <c r="F6" s="77">
         <v>46151</v>
       </c>
-      <c r="G5" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="75">
+      <c r="G6" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="75">
         <v>46035</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B7" s="75">
         <v>46035</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="28">
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="28">
         <v>38</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F7" s="75">
         <v>46096</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>16</v>
+      <c r="G7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1505,28 +1548,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="19.899999999999999" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
     </row>
     <row r="2" spans="1:19" ht="19.899999999999999" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
     </row>
     <row r="3" spans="1:19" ht="19.899999999999999" customHeight="1">
       <c r="A3" s="76"/>
@@ -1586,10 +1629,10 @@
         <v>45910</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" s="67">
         <v>2</v>
@@ -1598,10 +1641,10 @@
         <v>45975</v>
       </c>
       <c r="G5" s="68" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H5" s="68" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I5" s="68"/>
       <c r="J5"/>
@@ -1623,10 +1666,10 @@
         <v>45903</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="67">
         <v>105</v>
@@ -1635,13 +1678,13 @@
         <v>45964</v>
       </c>
       <c r="G6" s="66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" s="66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I6" s="66" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -1662,10 +1705,10 @@
         <v>45816</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="67">
         <v>125</v>
@@ -1674,10 +1717,10 @@
         <v>45874</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H7" s="66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1699,10 +1742,10 @@
         <v>45736</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="67">
         <v>20</v>
@@ -1711,10 +1754,10 @@
         <v>45800</v>
       </c>
       <c r="G8" s="66" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1736,20 +1779,20 @@
         <v>45694</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="68"/>
       <c r="F9" s="68">
         <v>45815</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1791,28 +1834,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
     </row>
     <row r="3" spans="1:19" ht="31.5">
       <c r="A3" s="76"/>
@@ -1872,10 +1915,10 @@
         <v>45621</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="38">
         <v>796</v>
@@ -1884,10 +1927,10 @@
         <v>45682</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I5" s="38"/>
     </row>
@@ -1899,10 +1942,10 @@
         <v>45617</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="38">
         <v>121</v>
@@ -1911,10 +1954,10 @@
         <v>45681</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="34"/>
@@ -1936,10 +1979,10 @@
         <v>45608</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="38">
         <v>136</v>
@@ -1948,13 +1991,13 @@
         <v>45726</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
@@ -1975,22 +2018,22 @@
         <v>45572</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="38">
         <v>632</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
@@ -2012,10 +2055,10 @@
         <v>45567</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="E9" s="38">
         <v>1</v>
@@ -2024,7 +2067,7 @@
         <v>45626</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
@@ -2037,20 +2080,20 @@
         <v>45560</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="38">
         <v>13</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I10" s="38"/>
     </row>
@@ -2062,20 +2105,20 @@
         <v>45526</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="38">
         <v>117</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I11" s="38"/>
     </row>
@@ -2087,10 +2130,10 @@
         <v>45504</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" s="38">
         <v>205</v>
@@ -2099,10 +2142,10 @@
         <v>45658</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I12" s="38"/>
     </row>
@@ -2114,10 +2157,10 @@
         <v>45485</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" s="38">
         <v>58</v>
@@ -2126,10 +2169,10 @@
         <v>45541</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I13" s="38"/>
     </row>
@@ -2141,10 +2184,10 @@
         <v>45432</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" s="38">
         <v>30</v>
@@ -2153,27 +2196,27 @@
         <v>45488</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="40">
         <v>45421</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" s="38">
         <v>1029</v>
@@ -2182,13 +2225,13 @@
         <v>45473</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2199,22 +2242,22 @@
         <v>45414</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" s="38">
         <v>36</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I16" s="38"/>
     </row>
@@ -2226,22 +2269,22 @@
         <v>45383</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="40">
         <v>45412</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I17" s="38"/>
     </row>
@@ -2253,10 +2296,10 @@
         <v>45383</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" s="38">
         <v>1</v>
@@ -2265,10 +2308,10 @@
         <v>45443</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I18" s="38"/>
     </row>
@@ -2280,10 +2323,10 @@
         <v>45349</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" s="38">
         <v>48</v>
@@ -2292,10 +2335,10 @@
         <v>45611</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I19" s="38"/>
     </row>
@@ -2307,10 +2350,10 @@
         <v>45328</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E20" s="38">
         <v>130</v>
@@ -2319,13 +2362,13 @@
         <v>45384</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2336,10 +2379,10 @@
         <v>45316</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" s="38">
         <v>1</v>
@@ -2348,10 +2391,10 @@
         <v>45316</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I21" s="40"/>
     </row>
@@ -3402,28 +3445,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="76"/>
@@ -3444,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>4</v>
@@ -3473,10 +3516,10 @@
         <v>45191</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="6">
         <v>136</v>
@@ -3485,10 +3528,10 @@
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I5" s="17"/>
     </row>
@@ -3500,22 +3543,22 @@
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I6" s="17"/>
     </row>
@@ -3527,10 +3570,10 @@
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" s="38">
         <v>52</v>
@@ -3539,10 +3582,10 @@
         <v>45153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3553,10 +3596,10 @@
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6">
         <v>211</v>
@@ -3565,13 +3608,13 @@
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3582,10 +3625,10 @@
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" s="6">
         <v>249</v>
@@ -3594,13 +3637,13 @@
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3611,10 +3654,10 @@
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E10" s="6">
         <v>169</v>
@@ -3623,13 +3666,13 @@
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3640,10 +3683,10 @@
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="6">
         <v>75</v>
@@ -3652,13 +3695,13 @@
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="5" customFormat="1" ht="15">
@@ -3669,10 +3712,10 @@
         <v>44937</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" s="38">
         <v>81</v>
@@ -3681,10 +3724,10 @@
         <v>44990</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I12" s="17"/>
     </row>
@@ -3696,10 +3739,10 @@
         <v>44831</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" s="63">
         <v>1</v>
@@ -3708,10 +3751,10 @@
         <v>44890</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I13" s="8"/>
     </row>
@@ -3723,10 +3766,10 @@
         <v>44817</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E14" s="63">
         <v>77</v>
@@ -3735,10 +3778,10 @@
         <v>44880</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I14" s="22"/>
     </row>
@@ -3750,10 +3793,10 @@
         <v>44594</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="64">
         <v>198</v>
@@ -3762,10 +3805,10 @@
         <v>44659</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3776,10 +3819,10 @@
         <v>44336</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" s="64">
         <v>94</v>
@@ -3788,13 +3831,13 @@
         <v>44394</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3805,10 +3848,10 @@
         <v>44342</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E17" s="64">
         <v>464</v>
@@ -3817,10 +3860,10 @@
         <v>44403</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3831,10 +3874,10 @@
         <v>44104</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" s="64">
         <v>13</v>
@@ -3843,10 +3886,10 @@
         <v>44104</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3857,10 +3900,10 @@
         <v>44068</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="64">
         <v>40</v>
@@ -3869,10 +3912,10 @@
         <v>44061</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3883,10 +3926,10 @@
         <v>44060</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20" s="64">
         <v>106</v>
@@ -3895,10 +3938,10 @@
         <v>44057</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3909,10 +3952,10 @@
         <v>44056</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" s="64">
         <v>272</v>
@@ -3921,13 +3964,13 @@
         <v>43914</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3938,10 +3981,10 @@
         <v>44040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="64">
         <v>1043</v>
@@ -3950,13 +3993,13 @@
         <v>44104</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3967,10 +4010,10 @@
         <v>44040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="64">
         <v>296</v>
@@ -3979,13 +4022,13 @@
         <v>44104</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -3996,10 +4039,10 @@
         <v>44042</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24" s="64">
         <v>73</v>
@@ -4008,10 +4051,10 @@
         <v>44075</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4022,10 +4065,10 @@
         <v>44022</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" s="64">
         <v>127</v>
@@ -4034,13 +4077,13 @@
         <v>44044</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4051,10 +4094,10 @@
         <v>44004</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E26" s="64">
         <v>71</v>
@@ -4063,10 +4106,10 @@
         <v>43973</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4077,10 +4120,10 @@
         <v>44012</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E27" s="64">
         <v>65</v>
@@ -4089,10 +4132,10 @@
         <v>44012</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4103,10 +4146,10 @@
         <v>43985</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E28" s="64">
         <v>65</v>
@@ -4115,10 +4158,10 @@
         <v>43904</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4129,10 +4172,10 @@
         <v>43980</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" s="64">
         <v>231</v>
@@ -4141,10 +4184,10 @@
         <v>43980</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4155,10 +4198,10 @@
         <v>44068</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" s="64">
         <v>72</v>
@@ -4167,10 +4210,10 @@
         <v>43958</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4181,10 +4224,10 @@
         <v>43948</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E31" s="64">
         <v>136</v>
@@ -4193,10 +4236,10 @@
         <v>43906</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4207,10 +4250,10 @@
         <v>43942</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E32" s="64">
         <v>5</v>
@@ -4219,10 +4262,10 @@
         <v>43942</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4233,10 +4276,10 @@
         <v>43944</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E33" s="64">
         <v>1</v>
@@ -4245,10 +4288,10 @@
         <v>43941</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4259,10 +4302,10 @@
         <v>43938</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E34" s="64">
         <v>13</v>
@@ -4271,10 +4314,10 @@
         <v>43938</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4285,10 +4328,10 @@
         <v>43935</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E35" s="64">
         <v>51</v>
@@ -4297,10 +4340,10 @@
         <v>43906</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4311,10 +4354,10 @@
         <v>43925</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="64">
         <v>110</v>
@@ -4323,10 +4366,10 @@
         <v>43927</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4337,10 +4380,10 @@
         <v>43917</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E37" s="64">
         <v>37</v>
@@ -4349,10 +4392,10 @@
         <v>43916</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4363,10 +4406,10 @@
         <v>43913</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E38" s="64">
         <v>146</v>
@@ -4375,13 +4418,13 @@
         <v>43898</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4392,10 +4435,10 @@
         <v>43910</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="64">
         <v>87</v>
@@ -4404,10 +4447,10 @@
         <v>43910</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4418,10 +4461,10 @@
         <v>43913</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E40" s="64">
         <v>110</v>
@@ -4430,10 +4473,10 @@
         <v>43906</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4444,10 +4487,10 @@
         <v>43510</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E41" s="64">
         <v>1</v>
@@ -4456,10 +4499,10 @@
         <v>43567</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4470,22 +4513,22 @@
         <v>43486</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E42" s="64">
         <v>59</v>
       </c>
       <c r="F42" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4496,10 +4539,10 @@
         <v>43479</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E43" s="64">
         <v>62</v>
@@ -4508,10 +4551,10 @@
         <v>43542</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4522,10 +4565,10 @@
         <v>43413</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E44" s="64">
         <v>51</v>
@@ -4534,10 +4577,10 @@
         <v>43131</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4548,10 +4591,10 @@
         <v>43405</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E45" s="64">
         <v>92</v>
@@ -4560,10 +4603,10 @@
         <v>43465</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4574,10 +4617,10 @@
         <v>43405</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E46" s="64">
         <v>181</v>
@@ -4586,10 +4629,10 @@
         <v>43469</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4600,10 +4643,10 @@
         <v>43382</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E47" s="64">
         <v>180</v>
@@ -4612,10 +4655,10 @@
         <v>43382</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4626,10 +4669,10 @@
         <v>43363</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E48" s="64">
         <v>83</v>
@@ -4638,10 +4681,10 @@
         <v>43434</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4652,10 +4695,10 @@
         <v>43276</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E49" s="64">
         <v>64</v>
@@ -4664,13 +4707,13 @@
         <v>43339</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4681,10 +4724,10 @@
         <v>43252</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E50" s="64">
         <v>149</v>
@@ -4693,10 +4736,10 @@
         <v>43312</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4707,10 +4750,10 @@
         <v>43042</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E51" s="64">
         <v>477</v>
@@ -4719,13 +4762,13 @@
         <v>43112</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4736,22 +4779,22 @@
         <v>42990</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E52" s="64">
         <v>171</v>
       </c>
       <c r="F52" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4762,10 +4805,10 @@
         <v>42496</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E53" s="64">
         <v>187</v>
@@ -4774,10 +4817,10 @@
         <v>42492</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4788,10 +4831,10 @@
         <v>42495</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E54" s="64">
         <v>20</v>
@@ -4800,13 +4843,13 @@
         <v>42551</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4817,10 +4860,10 @@
         <v>42468</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E55" s="64">
         <v>154</v>
@@ -4829,10 +4872,10 @@
         <v>42528</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4843,22 +4886,22 @@
         <v>42401</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E56" s="64">
         <v>60</v>
       </c>
       <c r="F56" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4869,10 +4912,10 @@
         <v>42384</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E57" s="64">
         <v>131</v>
@@ -4881,10 +4924,10 @@
         <v>42405</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4895,22 +4938,22 @@
         <v>42326</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E58" s="64">
         <v>241</v>
       </c>
       <c r="F58" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4921,22 +4964,22 @@
         <v>42320</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E59" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F59" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4947,10 +4990,10 @@
         <v>42180</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E60" s="64">
         <v>70</v>
@@ -4959,10 +5002,10 @@
         <v>42240</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -4973,25 +5016,25 @@
         <v>42074</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E61" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F61" s="22">
         <v>42141</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5002,22 +5045,22 @@
         <v>42065</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E62" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F62" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5028,10 +5071,10 @@
         <v>41850</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E63" s="64">
         <v>5</v>
@@ -5040,10 +5083,10 @@
         <v>41912</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5054,10 +5097,10 @@
         <v>41821</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E64" s="64">
         <v>142</v>
@@ -5066,10 +5109,10 @@
         <v>41882</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5080,10 +5123,10 @@
         <v>41729</v>
       </c>
       <c r="C65" s="24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E65" s="64">
         <v>115</v>
@@ -5092,13 +5135,13 @@
         <v>41774</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5109,10 +5152,10 @@
         <v>41596</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E66" s="64">
         <v>49</v>
@@ -5121,10 +5164,10 @@
         <v>41654</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5135,10 +5178,10 @@
         <v>41547</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E67" s="64">
         <v>1</v>
@@ -5147,10 +5190,10 @@
         <v>41608</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5161,10 +5204,10 @@
         <v>41502</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E68" s="64">
         <v>66</v>
@@ -5173,10 +5216,10 @@
         <v>41555</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5187,10 +5230,10 @@
         <v>41438</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E69" s="64">
         <v>3</v>
@@ -5199,10 +5242,10 @@
         <v>41425</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5213,10 +5256,10 @@
         <v>41417</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E70" s="64">
         <v>62</v>
@@ -5225,10 +5268,10 @@
         <v>41485</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5239,22 +5282,22 @@
         <v>41285</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E71" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F71" s="22">
         <v>41347</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5265,10 +5308,10 @@
         <v>41087</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E72" s="64">
         <v>51</v>
@@ -5277,10 +5320,10 @@
         <v>41148</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5291,10 +5334,10 @@
         <v>41011</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E73" s="64">
         <v>150</v>
@@ -5303,13 +5346,13 @@
         <v>41071</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5320,10 +5363,10 @@
         <v>40939</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E74" s="64">
         <v>70</v>
@@ -5332,13 +5375,13 @@
         <v>41000</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5349,10 +5392,10 @@
         <v>40833</v>
       </c>
       <c r="C75" s="24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E75" s="64">
         <v>110</v>
@@ -5361,10 +5404,10 @@
         <v>40833</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I75" s="24"/>
     </row>
@@ -5376,10 +5419,10 @@
         <v>40788</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E76" s="64">
         <v>16</v>
@@ -5388,10 +5431,10 @@
         <v>40846</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I76" s="24"/>
     </row>
@@ -5403,10 +5446,10 @@
         <v>40758</v>
       </c>
       <c r="C77" s="24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E77" s="64">
         <v>9</v>
@@ -5415,10 +5458,10 @@
         <v>40816</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I77" s="24"/>
     </row>
@@ -5430,22 +5473,22 @@
         <v>40756</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E78" s="64">
         <v>98</v>
       </c>
       <c r="F78" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I78" s="24"/>
     </row>
@@ -5457,22 +5500,22 @@
         <v>40690</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E79" s="64">
         <v>21</v>
       </c>
       <c r="F79" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I79" s="24"/>
     </row>
@@ -5484,22 +5527,22 @@
         <v>40634</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E80" s="64">
         <v>98</v>
       </c>
       <c r="F80" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I80" s="24"/>
     </row>
@@ -5511,10 +5554,10 @@
         <v>40589</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E81" s="64">
         <v>5</v>
@@ -5523,10 +5566,10 @@
         <v>40644</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I81" s="24"/>
     </row>
@@ -5538,10 +5581,10 @@
         <v>40568</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E82" s="64">
         <v>122</v>
@@ -5550,10 +5593,10 @@
         <v>40592</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I82" s="24"/>
     </row>
@@ -5565,10 +5608,10 @@
         <v>40413</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E83" s="64">
         <v>89</v>
@@ -5577,10 +5620,10 @@
         <v>40452</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I83" s="24"/>
     </row>
@@ -5592,22 +5635,22 @@
         <v>40217</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D84" s="24" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E84" s="64">
         <v>26</v>
       </c>
       <c r="F84" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I84" s="24"/>
     </row>
@@ -5619,10 +5662,10 @@
         <v>40217</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E85" s="64">
         <v>165</v>
@@ -5631,10 +5674,10 @@
         <v>40217</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I85" s="24"/>
     </row>
@@ -5646,10 +5689,10 @@
         <v>40182</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E86" s="64">
         <v>8</v>
@@ -5658,10 +5701,10 @@
         <v>40210</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I86" s="24"/>
     </row>
@@ -5673,22 +5716,22 @@
         <v>40141</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E87" s="64">
         <v>66</v>
       </c>
       <c r="F87" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I87" s="24"/>
     </row>
@@ -5700,25 +5743,25 @@
         <v>40141</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E88" s="64">
         <v>103</v>
       </c>
       <c r="F88" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5729,22 +5772,22 @@
         <v>40094</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E89" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F89" s="22">
         <v>40147</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5755,10 +5798,10 @@
         <v>40091</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E90" s="64">
         <v>63</v>
@@ -5767,10 +5810,10 @@
         <v>40148</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5781,22 +5824,22 @@
         <v>40050</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E91" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F91" s="22">
         <v>39895</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5807,10 +5850,10 @@
         <v>40008</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E92" s="64">
         <v>130</v>
@@ -5819,10 +5862,10 @@
         <v>39895</v>
       </c>
       <c r="G92" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5833,10 +5876,10 @@
         <v>40008</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E93" s="64">
         <v>26</v>
@@ -5845,10 +5888,10 @@
         <v>40001</v>
       </c>
       <c r="G93" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5859,10 +5902,10 @@
         <v>39895</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E94" s="64">
         <v>14</v>
@@ -5871,10 +5914,10 @@
         <v>39895</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5885,10 +5928,10 @@
         <v>39996</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E95" s="64">
         <v>10</v>
@@ -5897,10 +5940,10 @@
         <v>40041</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:9" s="5" customFormat="1" ht="14.25">
@@ -5911,10 +5954,10 @@
         <v>39932</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E96" s="64">
         <v>171</v>
@@ -5923,13 +5966,13 @@
         <v>39994</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -5940,10 +5983,10 @@
         <v>39918</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E97" s="64">
         <v>55</v>
@@ -5952,10 +5995,10 @@
         <v>39994</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -5966,10 +6009,10 @@
         <v>39882</v>
       </c>
       <c r="C98" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D98" s="24" t="s">
         <v>83</v>
-      </c>
-      <c r="D98" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="E98" s="64">
         <v>29</v>
@@ -5978,10 +6021,10 @@
         <v>39943</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -5992,10 +6035,10 @@
         <v>39881</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E99" s="64">
         <v>71</v>
@@ -6004,10 +6047,10 @@
         <v>39941</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -6018,10 +6061,10 @@
         <v>39878</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D100" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E100" s="64">
         <v>54</v>
@@ -6030,10 +6073,10 @@
         <v>39935</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -6044,10 +6087,10 @@
         <v>39877</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D101" s="24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E101" s="64">
         <v>119</v>
@@ -6056,10 +6099,10 @@
         <v>39943</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -6070,10 +6113,10 @@
         <v>39864</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D102" s="24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E102" s="64">
         <v>270</v>
@@ -6082,10 +6125,10 @@
         <v>39828</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:14" s="5" customFormat="1" ht="14.25">
@@ -6096,10 +6139,10 @@
         <v>39825</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D103" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E103" s="64">
         <v>121</v>
@@ -6108,10 +6151,10 @@
         <v>39821</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -7281,9 +7324,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7431,16 +7477,13 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7448,5 +7491,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
 </file>
--- a/data/warn-scraper/cache/ri/WARN Report.xlsx
+++ b/data/warn-scraper/cache/ri/WARN Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75CB4929-1866-446D-A065-3EE9F4FF02C9}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4B8664-6BC9-4631-BCD3-307DA1D16A59}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="206">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -648,6 +648,15 @@
   </si>
   <si>
     <t>East Providence and Providence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideal US Talent Systems Worker OpCo LLC </t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
   </si>
 </sst>
 </file>
@@ -794,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -903,7 +912,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -916,11 +924,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -933,10 +938,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -995,7 +999,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1016,6 +1020,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,9 +1044,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1074,7 +1084,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1180,7 +1190,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1322,7 +1332,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1330,81 +1340,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="13.09765625" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" customWidth="1"/>
+    <col min="7" max="7" width="20.19921875" customWidth="1"/>
+    <col min="8" max="8" width="16.8984375" customWidth="1"/>
     <col min="9" max="9" width="51.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="86"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.5">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="76"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.2">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-    </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="22.15" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A4" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="G4" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="76" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1418,105 +1428,128 @@
       <c r="R4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="1:19" s="59" customFormat="1" ht="22.15" customHeight="1">
-      <c r="A5" s="77">
+    <row r="5" spans="1:19" ht="31.2">
+      <c r="A5" s="72">
+        <v>46143</v>
+      </c>
+      <c r="B5" s="72">
+        <v>46147</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="72">
+        <v>46204</v>
+      </c>
+      <c r="H5" s="80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="54" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A6" s="72">
         <v>46107</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B6" s="72">
         <v>46112</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C6" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D6" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="85">
+      <c r="E6" s="80">
         <v>154</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F6" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="85" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-    </row>
-    <row r="6" spans="1:19" s="80" customFormat="1" ht="32.25">
-      <c r="A6" s="77">
+      <c r="G6" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="73"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="74"/>
+    </row>
+    <row r="7" spans="1:19" s="75" customFormat="1" ht="31.2">
+      <c r="A7" s="72">
         <v>46100</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B7" s="72">
         <v>46100</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C7" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D7" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="85">
+      <c r="E7" s="80">
         <v>52</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F7" s="72">
         <v>46151</v>
       </c>
-      <c r="G6" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="78" t="s">
+      <c r="G7" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="75">
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="74"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="70">
         <v>46035</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B8" s="70">
         <v>46035</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E8" s="28">
         <v>38</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F8" s="70">
         <v>46096</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="28" t="s">
+      <c r="G8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1534,80 +1567,80 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19.899999999999999" customHeight="1">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:19" ht="19.95" customHeight="1">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-    </row>
-    <row r="2" spans="1:19" ht="19.899999999999999" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-    </row>
-    <row r="3" spans="1:19" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="76"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+    </row>
+    <row r="2" spans="1:19" ht="19.95" customHeight="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.95" customHeight="1">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-    </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.899999999999999" customHeight="1">
-      <c r="A4" s="70" t="s">
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.95" customHeight="1">
+      <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1621,32 +1654,32 @@
       <c r="R4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="1:19" s="59" customFormat="1" ht="36" customHeight="1">
-      <c r="A5" s="68">
+    <row r="5" spans="1:19" s="54" customFormat="1" ht="36" customHeight="1">
+      <c r="A5" s="63">
         <v>45910</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="63">
         <v>45910</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="62">
         <v>2</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="63">
         <v>45975</v>
       </c>
-      <c r="G5" s="68" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="68"/>
+      <c r="G5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="63"/>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
@@ -1658,32 +1691,32 @@
       <c r="R5"/>
       <c r="S5"/>
     </row>
-    <row r="6" spans="1:19" s="59" customFormat="1">
-      <c r="A6" s="68">
+    <row r="6" spans="1:19" s="54" customFormat="1">
+      <c r="A6" s="63">
         <v>45898</v>
       </c>
-      <c r="B6" s="68">
+      <c r="B6" s="63">
         <v>45903</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="66" t="s">
+      <c r="D6" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="67">
+      <c r="E6" s="62">
         <v>105</v>
       </c>
-      <c r="F6" s="68">
+      <c r="F6" s="63">
         <v>45964</v>
       </c>
-      <c r="G6" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="66" t="s">
+      <c r="G6" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="61" t="s">
         <v>24</v>
       </c>
       <c r="J6"/>
@@ -1697,29 +1730,29 @@
       <c r="R6"/>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" s="59" customFormat="1" ht="31.5">
-      <c r="A7" s="68">
+    <row r="7" spans="1:19" s="54" customFormat="1" ht="31.2">
+      <c r="A7" s="63">
         <v>45814</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="63">
         <v>45816</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="62">
         <v>125</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="63">
         <v>45874</v>
       </c>
-      <c r="G7" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="66" t="s">
+      <c r="G7" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="61" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1734,29 +1767,29 @@
       <c r="R7"/>
       <c r="S7"/>
     </row>
-    <row r="8" spans="1:19" s="59" customFormat="1">
-      <c r="A8" s="68">
+    <row r="8" spans="1:19" s="54" customFormat="1">
+      <c r="A8" s="63">
         <v>45736</v>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="63">
         <v>45736</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="62">
         <v>20</v>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="63">
         <v>45800</v>
       </c>
-      <c r="G8" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="66" t="s">
+      <c r="G8" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="61" t="s">
         <v>14</v>
       </c>
       <c r="I8"/>
@@ -1771,27 +1804,27 @@
       <c r="R8"/>
       <c r="S8"/>
     </row>
-    <row r="9" spans="1:19" s="65" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A9" s="68">
+    <row r="9" spans="1:19" s="60" customFormat="1" ht="33.75" customHeight="1">
+      <c r="A9" s="63">
         <v>45692</v>
       </c>
-      <c r="B9" s="68">
+      <c r="B9" s="63">
         <v>45694</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68">
+      <c r="E9" s="63"/>
+      <c r="F9" s="63">
         <v>45815</v>
       </c>
-      <c r="G9" s="68" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="68" t="s">
+      <c r="G9" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="63" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="38"/>
@@ -1820,80 +1853,80 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S123"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="49.5" style="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="28.375" style="51" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.3984375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.625" customWidth="1"/>
+    <col min="9" max="9" width="71.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="86"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.5">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="76"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.2">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-    </row>
-    <row r="4" spans="1:19" s="59" customFormat="1" ht="19.899999999999999" customHeight="1">
-      <c r="A4" s="70" t="s">
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.95" customHeight="1">
+      <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1914,7 +1947,7 @@
       <c r="B5" s="40">
         <v>45621</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="38" t="s">
@@ -1941,7 +1974,7 @@
       <c r="B6" s="33">
         <v>45617</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="38" t="s">
@@ -1978,7 +2011,7 @@
       <c r="B7" s="33">
         <v>45608</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="38" t="s">
@@ -2017,7 +2050,7 @@
       <c r="B8" s="33">
         <v>45572</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="38" t="s">
@@ -2054,7 +2087,7 @@
       <c r="B9" s="40">
         <v>45567</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="38" t="s">
@@ -2079,7 +2112,7 @@
       <c r="B10" s="40">
         <v>45560</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="38" t="s">
@@ -2104,7 +2137,7 @@
       <c r="B11" s="40">
         <v>45526</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="38" t="s">
@@ -2129,7 +2162,7 @@
       <c r="B12" s="40">
         <v>45504</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="38" t="s">
@@ -2156,7 +2189,7 @@
       <c r="B13" s="40">
         <v>45485</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="38" t="s">
@@ -2183,7 +2216,7 @@
       <c r="B14" s="40">
         <v>45432</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="38" t="s">
@@ -2212,7 +2245,7 @@
       <c r="B15" s="40">
         <v>45421</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="38" t="s">
@@ -2241,7 +2274,7 @@
       <c r="B16" s="40">
         <v>45414</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="38" t="s">
@@ -2268,7 +2301,7 @@
       <c r="B17" s="40">
         <v>45383</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="38" t="s">
@@ -2295,7 +2328,7 @@
       <c r="B18" s="40">
         <v>45383</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="38" t="s">
@@ -2322,7 +2355,7 @@
       <c r="B19" s="40">
         <v>45349</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D19" s="38" t="s">
@@ -2349,7 +2382,7 @@
       <c r="B20" s="40">
         <v>45328</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D20" s="38" t="s">
@@ -2378,7 +2411,7 @@
       <c r="B21" s="40">
         <v>45316</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="5" t="s">
         <v>60</v>
       </c>
       <c r="D21" s="38" t="s">
@@ -2400,41 +2433,41 @@
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="15">
       <c r="B22" s="11"/>
-      <c r="C22" s="53"/>
+      <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="15"/>
-      <c r="F22" s="43"/>
+      <c r="F22" s="42"/>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="15">
       <c r="B23" s="11"/>
-      <c r="C23" s="53"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="15"/>
-      <c r="F23" s="43"/>
+      <c r="F23" s="42"/>
     </row>
     <row r="24" spans="1:9" s="5" customFormat="1" ht="18.600000000000001" customHeight="1">
       <c r="B24" s="11"/>
-      <c r="C24" s="53"/>
+      <c r="C24" s="49"/>
       <c r="D24" s="12"/>
       <c r="E24" s="15"/>
-      <c r="F24" s="43"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="B25" s="11"/>
-      <c r="C25" s="53"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="12"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="43"/>
+      <c r="F25" s="42"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="B26" s="11"/>
-      <c r="C26" s="53"/>
+      <c r="C26" s="49"/>
       <c r="D26" s="12"/>
       <c r="E26" s="15"/>
-      <c r="F26" s="43"/>
+      <c r="F26" s="42"/>
       <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" s="5" customFormat="1" ht="15">
@@ -2442,7 +2475,7 @@
       <c r="C27" s="36"/>
       <c r="D27" s="20"/>
       <c r="E27" s="29"/>
-      <c r="F27" s="44"/>
+      <c r="F27" s="43"/>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
       <c r="I27" s="8"/>
@@ -2450,10 +2483,10 @@
     <row r="28" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A28" s="11"/>
       <c r="B28" s="19"/>
-      <c r="C28" s="54"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="19"/>
       <c r="E28" s="29"/>
-      <c r="F28" s="44"/>
+      <c r="F28" s="43"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
@@ -2461,20 +2494,20 @@
     <row r="29" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A29" s="11"/>
       <c r="B29" s="19"/>
-      <c r="C29" s="55"/>
+      <c r="C29" s="51"/>
       <c r="D29" s="23"/>
       <c r="E29" s="30"/>
-      <c r="F29" s="44"/>
+      <c r="F29" s="43"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
     </row>
     <row r="30" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A30" s="11"/>
       <c r="B30" s="19"/>
-      <c r="C30" s="55"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="23"/>
       <c r="E30" s="30"/>
-      <c r="F30" s="44"/>
+      <c r="F30" s="43"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
       <c r="I30" s="24"/>
@@ -2482,50 +2515,50 @@
     <row r="31" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A31" s="18"/>
       <c r="B31" s="19"/>
-      <c r="C31" s="55"/>
+      <c r="C31" s="51"/>
       <c r="D31" s="23"/>
       <c r="E31" s="30"/>
-      <c r="F31" s="44"/>
+      <c r="F31" s="43"/>
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A32" s="11"/>
       <c r="B32" s="19"/>
-      <c r="C32" s="55"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="23"/>
       <c r="E32" s="30"/>
-      <c r="F32" s="44"/>
+      <c r="F32" s="43"/>
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
     </row>
     <row r="33" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
-      <c r="C33" s="55"/>
+      <c r="C33" s="51"/>
       <c r="D33" s="23"/>
       <c r="E33" s="30"/>
-      <c r="F33" s="44"/>
+      <c r="F33" s="43"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
     </row>
     <row r="34" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A34" s="19"/>
       <c r="B34" s="19"/>
-      <c r="C34" s="55"/>
+      <c r="C34" s="51"/>
       <c r="D34" s="23"/>
       <c r="E34" s="30"/>
-      <c r="F34" s="44"/>
+      <c r="F34" s="43"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24"/>
     </row>
     <row r="35" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A35" s="19"/>
       <c r="B35" s="19"/>
-      <c r="C35" s="55"/>
+      <c r="C35" s="51"/>
       <c r="D35" s="23"/>
       <c r="E35" s="30"/>
-      <c r="F35" s="44"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -2533,10 +2566,10 @@
     <row r="36" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
-      <c r="C36" s="55"/>
+      <c r="C36" s="51"/>
       <c r="D36" s="23"/>
       <c r="E36" s="30"/>
-      <c r="F36" s="44"/>
+      <c r="F36" s="43"/>
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -2544,10 +2577,10 @@
     <row r="37" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
-      <c r="C37" s="55"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="23"/>
       <c r="E37" s="30"/>
-      <c r="F37" s="44"/>
+      <c r="F37" s="43"/>
       <c r="G37" s="24"/>
       <c r="H37" s="24"/>
       <c r="I37" s="24"/>
@@ -2555,20 +2588,20 @@
     <row r="38" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A38" s="19"/>
       <c r="B38" s="19"/>
-      <c r="C38" s="55"/>
+      <c r="C38" s="51"/>
       <c r="D38" s="23"/>
       <c r="E38" s="30"/>
-      <c r="F38" s="44"/>
+      <c r="F38" s="43"/>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
     </row>
     <row r="39" spans="1:9" s="5" customFormat="1" ht="15">
       <c r="A39" s="19"/>
       <c r="B39" s="19"/>
-      <c r="C39" s="55"/>
+      <c r="C39" s="51"/>
       <c r="D39" s="23"/>
       <c r="E39" s="30"/>
-      <c r="F39" s="44"/>
+      <c r="F39" s="43"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
       <c r="I39" s="24"/>
@@ -2576,130 +2609,130 @@
     <row r="40" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A40" s="19"/>
       <c r="B40" s="13"/>
-      <c r="C40" s="55"/>
+      <c r="C40" s="51"/>
       <c r="D40" s="14"/>
       <c r="E40" s="16"/>
-      <c r="F40" s="45"/>
+      <c r="F40" s="44"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A41" s="19"/>
       <c r="B41" s="13"/>
-      <c r="C41" s="55"/>
+      <c r="C41" s="51"/>
       <c r="D41" s="14"/>
       <c r="E41" s="16"/>
-      <c r="F41" s="45"/>
+      <c r="F41" s="44"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A42" s="19"/>
       <c r="B42" s="13"/>
-      <c r="C42" s="55"/>
+      <c r="C42" s="51"/>
       <c r="D42" s="14"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="45"/>
+      <c r="F42" s="44"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A43" s="19"/>
       <c r="B43" s="13"/>
-      <c r="C43" s="55"/>
+      <c r="C43" s="51"/>
       <c r="D43" s="14"/>
       <c r="E43" s="16"/>
-      <c r="F43" s="45"/>
+      <c r="F43" s="44"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A44" s="19"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="55"/>
+      <c r="C44" s="51"/>
       <c r="D44" s="14"/>
       <c r="E44" s="16"/>
-      <c r="F44" s="45"/>
+      <c r="F44" s="44"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A45" s="19"/>
       <c r="B45" s="13"/>
-      <c r="C45" s="55"/>
+      <c r="C45" s="51"/>
       <c r="D45" s="14"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="45"/>
+      <c r="F45" s="44"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
-      <c r="C46" s="55"/>
+      <c r="C46" s="51"/>
       <c r="D46" s="14"/>
       <c r="E46" s="16"/>
-      <c r="F46" s="45"/>
+      <c r="F46" s="44"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
-      <c r="C47" s="55"/>
+      <c r="C47" s="51"/>
       <c r="D47" s="14"/>
       <c r="E47" s="16"/>
-      <c r="F47" s="45"/>
+      <c r="F47" s="44"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
-      <c r="C48" s="55"/>
+      <c r="C48" s="51"/>
       <c r="D48" s="14"/>
       <c r="E48" s="16"/>
-      <c r="F48" s="45"/>
+      <c r="F48" s="44"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
-      <c r="C49" s="55"/>
+      <c r="C49" s="51"/>
       <c r="D49" s="14"/>
       <c r="E49" s="16"/>
-      <c r="F49" s="45"/>
+      <c r="F49" s="44"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A50" s="10"/>
       <c r="B50" s="13"/>
-      <c r="C50" s="55"/>
+      <c r="C50" s="51"/>
       <c r="D50" s="14"/>
       <c r="E50" s="16"/>
-      <c r="F50" s="45"/>
+      <c r="F50" s="44"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A51" s="10"/>
       <c r="B51" s="13"/>
-      <c r="C51" s="55"/>
+      <c r="C51" s="51"/>
       <c r="D51" s="14"/>
       <c r="E51" s="16"/>
-      <c r="F51" s="45"/>
+      <c r="F51" s="44"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A52" s="10"/>
       <c r="B52" s="13"/>
-      <c r="C52" s="55"/>
+      <c r="C52" s="51"/>
       <c r="D52" s="14"/>
       <c r="E52" s="16"/>
-      <c r="F52" s="45"/>
+      <c r="F52" s="44"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
@@ -2707,110 +2740,110 @@
     <row r="53" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
-      <c r="C53" s="55"/>
+      <c r="C53" s="51"/>
       <c r="D53" s="14"/>
       <c r="E53" s="16"/>
-      <c r="F53" s="45"/>
+      <c r="F53" s="44"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
     </row>
     <row r="54" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
-      <c r="C54" s="55"/>
+      <c r="C54" s="51"/>
       <c r="D54" s="14"/>
       <c r="E54" s="16"/>
-      <c r="F54" s="45"/>
+      <c r="F54" s="44"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
-      <c r="C55" s="55"/>
+      <c r="C55" s="51"/>
       <c r="D55" s="14"/>
       <c r="E55" s="16"/>
-      <c r="F55" s="45"/>
+      <c r="F55" s="44"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A56" s="13"/>
       <c r="B56" s="13"/>
-      <c r="C56" s="55"/>
+      <c r="C56" s="51"/>
       <c r="D56" s="14"/>
       <c r="E56" s="16"/>
-      <c r="F56" s="46"/>
+      <c r="F56" s="45"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
-      <c r="C57" s="55"/>
+      <c r="C57" s="51"/>
       <c r="D57" s="14"/>
       <c r="E57" s="16"/>
-      <c r="F57" s="45"/>
+      <c r="F57" s="44"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
     </row>
     <row r="58" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A58" s="13"/>
       <c r="B58" s="7"/>
-      <c r="C58" s="56"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="9"/>
       <c r="E58" s="26"/>
-      <c r="F58" s="47"/>
+      <c r="F58" s="46"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A59" s="13"/>
       <c r="B59" s="7"/>
-      <c r="C59" s="56"/>
+      <c r="C59" s="52"/>
       <c r="D59" s="9"/>
       <c r="E59" s="26"/>
-      <c r="F59" s="47"/>
+      <c r="F59" s="46"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
     </row>
     <row r="60" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A60" s="13"/>
       <c r="B60" s="7"/>
-      <c r="C60" s="56"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="9"/>
       <c r="E60" s="26"/>
-      <c r="F60" s="47"/>
+      <c r="F60" s="46"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
     </row>
     <row r="61" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A61" s="13"/>
       <c r="B61" s="7"/>
-      <c r="C61" s="56"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="9"/>
       <c r="E61" s="26"/>
-      <c r="F61" s="47"/>
+      <c r="F61" s="46"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A62" s="13"/>
       <c r="B62" s="7"/>
-      <c r="C62" s="56"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="9"/>
       <c r="E62" s="26"/>
-      <c r="F62" s="47"/>
+      <c r="F62" s="46"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A63" s="13"/>
       <c r="B63" s="7"/>
-      <c r="C63" s="56"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="9"/>
       <c r="E63" s="26"/>
-      <c r="F63" s="47"/>
+      <c r="F63" s="46"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="9"/>
@@ -2818,20 +2851,20 @@
     <row r="64" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
-      <c r="C64" s="56"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="9"/>
       <c r="E64" s="26"/>
-      <c r="F64" s="47"/>
+      <c r="F64" s="46"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
     </row>
     <row r="65" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
-      <c r="C65" s="56"/>
+      <c r="C65" s="52"/>
       <c r="D65" s="9"/>
       <c r="E65" s="26"/>
-      <c r="F65" s="47"/>
+      <c r="F65" s="46"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
@@ -2839,30 +2872,30 @@
     <row r="66" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
-      <c r="C66" s="56"/>
+      <c r="C66" s="52"/>
       <c r="D66" s="9"/>
       <c r="E66" s="26"/>
-      <c r="F66" s="48"/>
+      <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
     </row>
     <row r="67" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
-      <c r="C67" s="56"/>
+      <c r="C67" s="52"/>
       <c r="D67" s="9"/>
       <c r="E67" s="26"/>
-      <c r="F67" s="47"/>
+      <c r="F67" s="46"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
-      <c r="C68" s="56"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="9"/>
       <c r="E68" s="26"/>
-      <c r="F68" s="47"/>
+      <c r="F68" s="46"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
@@ -2870,70 +2903,70 @@
     <row r="69" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
-      <c r="C69" s="56"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="9"/>
       <c r="E69" s="26"/>
-      <c r="F69" s="47"/>
+      <c r="F69" s="46"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
-      <c r="C70" s="56"/>
+      <c r="C70" s="52"/>
       <c r="D70" s="9"/>
       <c r="E70" s="26"/>
-      <c r="F70" s="48"/>
+      <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
-      <c r="C71" s="56"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="9"/>
       <c r="E71" s="26"/>
-      <c r="F71" s="47"/>
+      <c r="F71" s="46"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
     </row>
     <row r="72" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
-      <c r="C72" s="56"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="9"/>
       <c r="E72" s="26"/>
-      <c r="F72" s="48"/>
+      <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
     </row>
     <row r="73" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
-      <c r="C73" s="56"/>
+      <c r="C73" s="52"/>
       <c r="D73" s="9"/>
       <c r="E73" s="26"/>
-      <c r="F73" s="48"/>
+      <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
     </row>
     <row r="74" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
-      <c r="C74" s="56"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="9"/>
       <c r="E74" s="26"/>
-      <c r="F74" s="47"/>
+      <c r="F74" s="46"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
     </row>
     <row r="75" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
-      <c r="C75" s="56"/>
+      <c r="C75" s="52"/>
       <c r="D75" s="9"/>
       <c r="E75" s="26"/>
-      <c r="F75" s="47"/>
+      <c r="F75" s="46"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
@@ -2941,30 +2974,30 @@
     <row r="76" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
-      <c r="C76" s="56"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="9"/>
       <c r="E76" s="26"/>
-      <c r="F76" s="48"/>
+      <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="1:9" s="4" customFormat="1" ht="15">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
-      <c r="C77" s="56"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="9"/>
       <c r="E77" s="26"/>
-      <c r="F77" s="47"/>
+      <c r="F77" s="46"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="7"/>
       <c r="B78" s="3"/>
-      <c r="C78" s="57"/>
+      <c r="C78" s="53"/>
       <c r="D78" s="1"/>
       <c r="E78" s="27"/>
-      <c r="F78" s="49"/>
+      <c r="F78" s="47"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="2"/>
@@ -2972,10 +3005,10 @@
     <row r="79" spans="1:9">
       <c r="A79" s="7"/>
       <c r="B79" s="3"/>
-      <c r="C79" s="57"/>
+      <c r="C79" s="53"/>
       <c r="D79" s="1"/>
       <c r="E79" s="27"/>
-      <c r="F79" s="49"/>
+      <c r="F79" s="47"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2983,10 +3016,10 @@
     <row r="80" spans="1:9">
       <c r="A80" s="7"/>
       <c r="B80" s="3"/>
-      <c r="C80" s="57"/>
+      <c r="C80" s="53"/>
       <c r="D80" s="1"/>
       <c r="E80" s="27"/>
-      <c r="F80" s="49"/>
+      <c r="F80" s="47"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="2"/>
@@ -2994,10 +3027,10 @@
     <row r="81" spans="1:9">
       <c r="A81" s="7"/>
       <c r="B81" s="3"/>
-      <c r="C81" s="57"/>
+      <c r="C81" s="53"/>
       <c r="D81" s="1"/>
       <c r="E81" s="27"/>
-      <c r="F81" s="49"/>
+      <c r="F81" s="47"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="2"/>
@@ -3005,10 +3038,10 @@
     <row r="82" spans="1:9">
       <c r="A82" s="7"/>
       <c r="B82" s="3"/>
-      <c r="C82" s="57"/>
+      <c r="C82" s="53"/>
       <c r="D82" s="1"/>
       <c r="E82" s="27"/>
-      <c r="F82" s="49"/>
+      <c r="F82" s="47"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="2"/>
@@ -3016,10 +3049,10 @@
     <row r="83" spans="1:9">
       <c r="A83" s="7"/>
       <c r="B83" s="3"/>
-      <c r="C83" s="57"/>
+      <c r="C83" s="53"/>
       <c r="D83" s="1"/>
       <c r="E83" s="27"/>
-      <c r="F83" s="49"/>
+      <c r="F83" s="47"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="2"/>
@@ -3027,10 +3060,10 @@
     <row r="84" spans="1:9">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
-      <c r="C84" s="57"/>
+      <c r="C84" s="53"/>
       <c r="D84" s="1"/>
       <c r="E84" s="27"/>
-      <c r="F84" s="49"/>
+      <c r="F84" s="47"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="2"/>
@@ -3038,10 +3071,10 @@
     <row r="85" spans="1:9">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
-      <c r="C85" s="57"/>
+      <c r="C85" s="53"/>
       <c r="D85" s="1"/>
       <c r="E85" s="27"/>
-      <c r="F85" s="49"/>
+      <c r="F85" s="47"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="2"/>
@@ -3049,10 +3082,10 @@
     <row r="86" spans="1:9">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
-      <c r="C86" s="57"/>
+      <c r="C86" s="53"/>
       <c r="D86" s="1"/>
       <c r="E86" s="27"/>
-      <c r="F86" s="49"/>
+      <c r="F86" s="47"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="2"/>
@@ -3060,10 +3093,10 @@
     <row r="87" spans="1:9">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
-      <c r="C87" s="57"/>
+      <c r="C87" s="53"/>
       <c r="D87" s="1"/>
       <c r="E87" s="27"/>
-      <c r="F87" s="49"/>
+      <c r="F87" s="47"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -3071,10 +3104,10 @@
     <row r="88" spans="1:9">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
-      <c r="C88" s="57"/>
+      <c r="C88" s="53"/>
       <c r="D88" s="1"/>
       <c r="E88" s="27"/>
-      <c r="F88" s="49"/>
+      <c r="F88" s="47"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -3082,10 +3115,10 @@
     <row r="89" spans="1:9">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
-      <c r="C89" s="57"/>
+      <c r="C89" s="53"/>
       <c r="D89" s="1"/>
       <c r="E89" s="27"/>
-      <c r="F89" s="49"/>
+      <c r="F89" s="47"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3093,10 +3126,10 @@
     <row r="90" spans="1:9">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
-      <c r="C90" s="57"/>
+      <c r="C90" s="53"/>
       <c r="D90" s="1"/>
       <c r="E90" s="27"/>
-      <c r="F90" s="49"/>
+      <c r="F90" s="47"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3104,10 +3137,10 @@
     <row r="91" spans="1:9">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
-      <c r="C91" s="57"/>
+      <c r="C91" s="53"/>
       <c r="D91" s="1"/>
       <c r="E91" s="27"/>
-      <c r="F91" s="49"/>
+      <c r="F91" s="47"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3115,10 +3148,10 @@
     <row r="92" spans="1:9">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
-      <c r="C92" s="57"/>
+      <c r="C92" s="53"/>
       <c r="D92" s="1"/>
       <c r="E92" s="27"/>
-      <c r="F92" s="50"/>
+      <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3126,10 +3159,10 @@
     <row r="93" spans="1:9">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
-      <c r="C93" s="57"/>
+      <c r="C93" s="53"/>
       <c r="D93" s="1"/>
       <c r="E93" s="27"/>
-      <c r="F93" s="50"/>
+      <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3137,10 +3170,10 @@
     <row r="94" spans="1:9">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
-      <c r="C94" s="57"/>
+      <c r="C94" s="53"/>
       <c r="D94" s="1"/>
       <c r="E94" s="27"/>
-      <c r="F94" s="50"/>
+      <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -3148,10 +3181,10 @@
     <row r="95" spans="1:9">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
-      <c r="C95" s="57"/>
+      <c r="C95" s="53"/>
       <c r="D95" s="1"/>
       <c r="E95" s="27"/>
-      <c r="F95" s="49"/>
+      <c r="F95" s="47"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -3159,10 +3192,10 @@
     <row r="96" spans="1:9">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
-      <c r="C96" s="57"/>
+      <c r="C96" s="53"/>
       <c r="D96" s="1"/>
       <c r="E96" s="27"/>
-      <c r="F96" s="49"/>
+      <c r="F96" s="47"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -3170,10 +3203,10 @@
     <row r="97" spans="1:9">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
-      <c r="C97" s="57"/>
+      <c r="C97" s="53"/>
       <c r="D97" s="1"/>
       <c r="E97" s="27"/>
-      <c r="F97" s="49"/>
+      <c r="F97" s="47"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -3181,10 +3214,10 @@
     <row r="98" spans="1:9">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
-      <c r="C98" s="57"/>
+      <c r="C98" s="53"/>
       <c r="D98" s="1"/>
       <c r="E98" s="27"/>
-      <c r="F98" s="50"/>
+      <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -3192,10 +3225,10 @@
     <row r="99" spans="1:9">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
-      <c r="C99" s="57"/>
+      <c r="C99" s="53"/>
       <c r="D99" s="1"/>
       <c r="E99" s="27"/>
-      <c r="F99" s="49"/>
+      <c r="F99" s="47"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -3203,10 +3236,10 @@
     <row r="100" spans="1:9">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
-      <c r="C100" s="57"/>
+      <c r="C100" s="53"/>
       <c r="D100" s="1"/>
       <c r="E100" s="27"/>
-      <c r="F100" s="49"/>
+      <c r="F100" s="47"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
@@ -3214,10 +3247,10 @@
     <row r="101" spans="1:9">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
-      <c r="C101" s="57"/>
+      <c r="C101" s="53"/>
       <c r="D101" s="1"/>
       <c r="E101" s="27"/>
-      <c r="F101" s="50"/>
+      <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
@@ -3225,10 +3258,10 @@
     <row r="102" spans="1:9">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
-      <c r="C102" s="57"/>
+      <c r="C102" s="53"/>
       <c r="D102" s="1"/>
       <c r="E102" s="27"/>
-      <c r="F102" s="50"/>
+      <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
@@ -3236,10 +3269,10 @@
     <row r="103" spans="1:9">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
-      <c r="C103" s="57"/>
+      <c r="C103" s="53"/>
       <c r="D103" s="1"/>
       <c r="E103" s="27"/>
-      <c r="F103" s="49"/>
+      <c r="F103" s="47"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
       <c r="I103" s="2"/>
@@ -3247,10 +3280,10 @@
     <row r="104" spans="1:9">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
-      <c r="C104" s="57"/>
+      <c r="C104" s="53"/>
       <c r="D104" s="1"/>
       <c r="E104" s="27"/>
-      <c r="F104" s="49"/>
+      <c r="F104" s="47"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
       <c r="I104" s="2"/>
@@ -3258,10 +3291,10 @@
     <row r="105" spans="1:9">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
-      <c r="C105" s="57"/>
+      <c r="C105" s="53"/>
       <c r="D105" s="1"/>
       <c r="E105" s="27"/>
-      <c r="F105" s="49"/>
+      <c r="F105" s="47"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
       <c r="I105" s="2"/>
@@ -3269,10 +3302,10 @@
     <row r="106" spans="1:9">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
-      <c r="C106" s="57"/>
+      <c r="C106" s="53"/>
       <c r="D106" s="1"/>
       <c r="E106" s="27"/>
-      <c r="F106" s="49"/>
+      <c r="F106" s="47"/>
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
       <c r="I106" s="2"/>
@@ -3280,10 +3313,10 @@
     <row r="107" spans="1:9">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
-      <c r="C107" s="57"/>
+      <c r="C107" s="53"/>
       <c r="D107" s="1"/>
       <c r="E107" s="27"/>
-      <c r="F107" s="49"/>
+      <c r="F107" s="47"/>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
       <c r="I107" s="2"/>
@@ -3291,10 +3324,10 @@
     <row r="108" spans="1:9">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
-      <c r="C108" s="57"/>
+      <c r="C108" s="53"/>
       <c r="D108" s="1"/>
       <c r="E108" s="27"/>
-      <c r="F108" s="49"/>
+      <c r="F108" s="47"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
       <c r="I108" s="2"/>
@@ -3302,10 +3335,10 @@
     <row r="109" spans="1:9">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
-      <c r="C109" s="57"/>
+      <c r="C109" s="53"/>
       <c r="D109" s="1"/>
       <c r="E109" s="27"/>
-      <c r="F109" s="49"/>
+      <c r="F109" s="47"/>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
       <c r="I109" s="2"/>
@@ -3313,10 +3346,10 @@
     <row r="110" spans="1:9">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
-      <c r="C110" s="57"/>
+      <c r="C110" s="53"/>
       <c r="D110" s="1"/>
       <c r="E110" s="27"/>
-      <c r="F110" s="49"/>
+      <c r="F110" s="47"/>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
@@ -3324,10 +3357,10 @@
     <row r="111" spans="1:9">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
-      <c r="C111" s="57"/>
+      <c r="C111" s="53"/>
       <c r="D111" s="1"/>
       <c r="E111" s="27"/>
-      <c r="F111" s="49"/>
+      <c r="F111" s="47"/>
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
       <c r="I111" s="2"/>
@@ -3335,10 +3368,10 @@
     <row r="112" spans="1:9">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
-      <c r="C112" s="57"/>
+      <c r="C112" s="53"/>
       <c r="D112" s="1"/>
       <c r="E112" s="27"/>
-      <c r="F112" s="49"/>
+      <c r="F112" s="47"/>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
       <c r="I112" s="2"/>
@@ -3346,10 +3379,10 @@
     <row r="113" spans="1:9">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
-      <c r="C113" s="57"/>
+      <c r="C113" s="53"/>
       <c r="D113" s="1"/>
       <c r="E113" s="27"/>
-      <c r="F113" s="49"/>
+      <c r="F113" s="47"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="2"/>
@@ -3357,10 +3390,10 @@
     <row r="114" spans="1:9">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
-      <c r="C114" s="57"/>
+      <c r="C114" s="53"/>
       <c r="D114" s="1"/>
       <c r="E114" s="27"/>
-      <c r="F114" s="49"/>
+      <c r="F114" s="47"/>
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="2"/>
@@ -3368,10 +3401,10 @@
     <row r="115" spans="1:9">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
-      <c r="C115" s="57"/>
+      <c r="C115" s="53"/>
       <c r="D115" s="1"/>
       <c r="E115" s="27"/>
-      <c r="F115" s="49"/>
+      <c r="F115" s="47"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="2"/>
@@ -3379,10 +3412,10 @@
     <row r="116" spans="1:9">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
-      <c r="C116" s="57"/>
+      <c r="C116" s="53"/>
       <c r="D116" s="1"/>
       <c r="E116" s="27"/>
-      <c r="F116" s="49"/>
+      <c r="F116" s="47"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="2"/>
@@ -3390,10 +3423,10 @@
     <row r="117" spans="1:9">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
-      <c r="C117" s="57"/>
+      <c r="C117" s="53"/>
       <c r="D117" s="1"/>
       <c r="E117" s="27"/>
-      <c r="F117" s="49"/>
+      <c r="F117" s="47"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="2"/>
@@ -3431,53 +3464,53 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="103.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="103.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-    </row>
-    <row r="3" spans="1:9" ht="31.5">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1">
       <c r="A4" s="35" t="s">
@@ -3508,14 +3541,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="15">
-      <c r="A5" s="60">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A5" s="55">
         <v>45191</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="55">
         <v>45191</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="56" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -3524,7 +3557,7 @@
       <c r="E5" s="6">
         <v>136</v>
       </c>
-      <c r="F5" s="60">
+      <c r="F5" s="55">
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -3535,11 +3568,11 @@
       </c>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="15">
-      <c r="A6" s="60">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A6" s="55">
         <v>45156</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="55">
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -3562,11 +3595,11 @@
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="14.25">
-      <c r="A7" s="60">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A7" s="55">
         <v>45191</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="55">
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -3588,11 +3621,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="14.25">
-      <c r="A8" s="60">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A8" s="55">
         <v>45156</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="55">
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -3604,7 +3637,7 @@
       <c r="E8" s="6">
         <v>211</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="55">
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -3617,11 +3650,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A9" s="40">
         <v>45153</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="55">
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -3633,7 +3666,7 @@
       <c r="E9" s="6">
         <v>249</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="55">
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -3646,11 +3679,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="14.25">
-      <c r="A10" s="60">
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A10" s="55">
         <v>45112</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="55">
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -3662,7 +3695,7 @@
       <c r="E10" s="6">
         <v>169</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="55">
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
@@ -3675,11 +3708,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="14.25">
-      <c r="A11" s="60">
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A11" s="55">
         <v>45107</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="55">
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -3691,7 +3724,7 @@
       <c r="E11" s="6">
         <v>75</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="55">
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -3704,8 +3737,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="15">
-      <c r="A12" s="60">
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A12" s="55">
         <v>45063</v>
       </c>
       <c r="B12" s="40">
@@ -3731,8 +3764,8 @@
       </c>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="14.25">
-      <c r="A13" s="62">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="13.8">
+      <c r="A13" s="57">
         <v>44949</v>
       </c>
       <c r="B13" s="22">
@@ -3744,7 +3777,7 @@
       <c r="D13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="58">
         <v>1</v>
       </c>
       <c r="F13" s="22">
@@ -3758,7 +3791,7 @@
       </c>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A14" s="40">
         <v>44930</v>
       </c>
@@ -3771,7 +3804,7 @@
       <c r="D14" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="58">
         <v>77</v>
       </c>
       <c r="F14" s="22">
@@ -3785,7 +3818,7 @@
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A15" s="22">
         <v>44827</v>
       </c>
@@ -3798,7 +3831,7 @@
       <c r="D15" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="59">
         <v>198</v>
       </c>
       <c r="F15" s="22">
@@ -3811,7 +3844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A16" s="22">
         <v>44817</v>
       </c>
@@ -3824,7 +3857,7 @@
       <c r="D16" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="59">
         <v>94</v>
       </c>
       <c r="F16" s="22">
@@ -3840,7 +3873,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="17" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A17" s="22">
         <v>44595</v>
       </c>
@@ -3853,7 +3886,7 @@
       <c r="D17" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="59">
         <v>464</v>
       </c>
       <c r="F17" s="22">
@@ -3866,7 +3899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A18" s="22">
         <v>44334</v>
       </c>
@@ -3879,7 +3912,7 @@
       <c r="D18" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="59">
         <v>13</v>
       </c>
       <c r="F18" s="22">
@@ -3892,7 +3925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="19" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A19" s="22">
         <v>44342</v>
       </c>
@@ -3905,7 +3938,7 @@
       <c r="D19" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="59">
         <v>40</v>
       </c>
       <c r="F19" s="22">
@@ -3918,7 +3951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="20" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A20" s="22">
         <v>44105</v>
       </c>
@@ -3931,7 +3964,7 @@
       <c r="D20" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="59">
         <v>106</v>
       </c>
       <c r="F20" s="22">
@@ -3944,7 +3977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A21" s="22">
         <v>44064</v>
       </c>
@@ -3957,7 +3990,7 @@
       <c r="D21" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="64">
+      <c r="E21" s="59">
         <v>272</v>
       </c>
       <c r="F21" s="22">
@@ -3973,7 +4006,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A22" s="22">
         <v>44057</v>
       </c>
@@ -3986,7 +4019,7 @@
       <c r="D22" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="64">
+      <c r="E22" s="59">
         <v>1043</v>
       </c>
       <c r="F22" s="22">
@@ -4002,7 +4035,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A23" s="22">
         <v>44049</v>
       </c>
@@ -4015,7 +4048,7 @@
       <c r="D23" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="59">
         <v>296</v>
       </c>
       <c r="F23" s="22">
@@ -4031,7 +4064,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A24" s="22">
         <v>44054</v>
       </c>
@@ -4044,7 +4077,7 @@
       <c r="D24" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="59">
         <v>73</v>
       </c>
       <c r="F24" s="22">
@@ -4057,7 +4090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A25" s="22">
         <v>44054</v>
       </c>
@@ -4070,7 +4103,7 @@
       <c r="D25" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="64">
+      <c r="E25" s="59">
         <v>127</v>
       </c>
       <c r="F25" s="22">
@@ -4086,7 +4119,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A26" s="22">
         <v>44046</v>
       </c>
@@ -4099,7 +4132,7 @@
       <c r="D26" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="59">
         <v>71</v>
       </c>
       <c r="F26" s="22">
@@ -4112,7 +4145,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A27" s="22">
         <v>44027</v>
       </c>
@@ -4125,7 +4158,7 @@
       <c r="D27" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="64">
+      <c r="E27" s="59">
         <v>65</v>
       </c>
       <c r="F27" s="22">
@@ -4138,7 +4171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A28" s="22">
         <v>44004</v>
       </c>
@@ -4151,7 +4184,7 @@
       <c r="D28" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="59">
         <v>65</v>
       </c>
       <c r="F28" s="22">
@@ -4164,7 +4197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="29" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A29" s="22">
         <v>44012</v>
       </c>
@@ -4177,7 +4210,7 @@
       <c r="D29" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="64">
+      <c r="E29" s="59">
         <v>231</v>
       </c>
       <c r="F29" s="22">
@@ -4190,7 +4223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A30" s="22">
         <v>43985</v>
       </c>
@@ -4203,7 +4236,7 @@
       <c r="D30" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="64">
+      <c r="E30" s="59">
         <v>72</v>
       </c>
       <c r="F30" s="22">
@@ -4216,7 +4249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A31" s="22">
         <v>43980</v>
       </c>
@@ -4229,7 +4262,7 @@
       <c r="D31" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="64">
+      <c r="E31" s="59">
         <v>136</v>
       </c>
       <c r="F31" s="22">
@@ -4242,7 +4275,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A32" s="40">
         <v>44063</v>
       </c>
@@ -4255,7 +4288,7 @@
       <c r="D32" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="64">
+      <c r="E32" s="59">
         <v>5</v>
       </c>
       <c r="F32" s="22">
@@ -4268,7 +4301,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A33" s="40">
         <v>43948</v>
       </c>
@@ -4281,7 +4314,7 @@
       <c r="D33" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="64">
+      <c r="E33" s="59">
         <v>1</v>
       </c>
       <c r="F33" s="22">
@@ -4294,7 +4327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A34" s="40">
         <v>43942</v>
       </c>
@@ -4307,7 +4340,7 @@
       <c r="D34" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="64">
+      <c r="E34" s="59">
         <v>13</v>
       </c>
       <c r="F34" s="22">
@@ -4320,7 +4353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="35" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A35" s="22">
         <v>43941</v>
       </c>
@@ -4333,7 +4366,7 @@
       <c r="D35" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="64">
+      <c r="E35" s="59">
         <v>51</v>
       </c>
       <c r="F35" s="22">
@@ -4346,7 +4379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="36" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A36" s="22">
         <v>43907</v>
       </c>
@@ -4359,7 +4392,7 @@
       <c r="D36" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="64">
+      <c r="E36" s="59">
         <v>110</v>
       </c>
       <c r="F36" s="22">
@@ -4372,7 +4405,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="37" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A37" s="22">
         <v>43927</v>
       </c>
@@ -4385,7 +4418,7 @@
       <c r="D37" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="64">
+      <c r="E37" s="59">
         <v>37</v>
       </c>
       <c r="F37" s="22">
@@ -4398,7 +4431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="38" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A38" s="22">
         <v>43925</v>
       </c>
@@ -4411,7 +4444,7 @@
       <c r="D38" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="64">
+      <c r="E38" s="59">
         <v>146</v>
       </c>
       <c r="F38" s="22">
@@ -4427,7 +4460,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="39" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A39" s="22">
         <v>43916</v>
       </c>
@@ -4440,7 +4473,7 @@
       <c r="D39" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="64">
+      <c r="E39" s="59">
         <v>87</v>
       </c>
       <c r="F39" s="22">
@@ -4453,7 +4486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="40" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A40" s="22">
         <v>43916</v>
       </c>
@@ -4466,7 +4499,7 @@
       <c r="D40" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="64">
+      <c r="E40" s="59">
         <v>110</v>
       </c>
       <c r="F40" s="22">
@@ -4479,7 +4512,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="41" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A41" s="22">
         <v>43910</v>
       </c>
@@ -4492,7 +4525,7 @@
       <c r="D41" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="64">
+      <c r="E41" s="59">
         <v>1</v>
       </c>
       <c r="F41" s="22">
@@ -4505,7 +4538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="42" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A42" s="22">
         <v>43909</v>
       </c>
@@ -4518,10 +4551,10 @@
       <c r="D42" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="64">
+      <c r="E42" s="59">
         <v>59</v>
       </c>
-      <c r="F42" s="64" t="s">
+      <c r="F42" s="59" t="s">
         <v>118</v>
       </c>
       <c r="G42" s="24" t="s">
@@ -4531,7 +4564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="43" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A43" s="22">
         <v>43509</v>
       </c>
@@ -4544,7 +4577,7 @@
       <c r="D43" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="64">
+      <c r="E43" s="59">
         <v>62</v>
       </c>
       <c r="F43" s="22">
@@ -4557,7 +4590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="44" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A44" s="22">
         <v>43486</v>
       </c>
@@ -4570,7 +4603,7 @@
       <c r="D44" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="64">
+      <c r="E44" s="59">
         <v>51</v>
       </c>
       <c r="F44" s="22">
@@ -4583,7 +4616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A45" s="22">
         <v>43479</v>
       </c>
@@ -4596,7 +4629,7 @@
       <c r="D45" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E45" s="64">
+      <c r="E45" s="59">
         <v>92</v>
       </c>
       <c r="F45" s="22">
@@ -4609,7 +4642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A46" s="22">
         <v>43405</v>
       </c>
@@ -4622,7 +4655,7 @@
       <c r="D46" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="64">
+      <c r="E46" s="59">
         <v>181</v>
       </c>
       <c r="F46" s="22">
@@ -4635,7 +4668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="47" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A47" s="22">
         <v>76277</v>
       </c>
@@ -4648,7 +4681,7 @@
       <c r="D47" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="64">
+      <c r="E47" s="59">
         <v>180</v>
       </c>
       <c r="F47" s="22">
@@ -4661,7 +4694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="48" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A48" s="22">
         <v>76268</v>
       </c>
@@ -4674,7 +4707,7 @@
       <c r="D48" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="64">
+      <c r="E48" s="59">
         <v>83</v>
       </c>
       <c r="F48" s="22">
@@ -4687,7 +4720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="49" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A49" s="22">
         <v>43382</v>
       </c>
@@ -4700,7 +4733,7 @@
       <c r="D49" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E49" s="64">
+      <c r="E49" s="59">
         <v>64</v>
       </c>
       <c r="F49" s="22">
@@ -4716,7 +4749,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="50" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A50" s="22">
         <v>43362</v>
       </c>
@@ -4729,7 +4762,7 @@
       <c r="D50" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="E50" s="64">
+      <c r="E50" s="59">
         <v>149</v>
       </c>
       <c r="F50" s="22">
@@ -4742,7 +4775,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="51" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A51" s="22">
         <v>43273</v>
       </c>
@@ -4755,7 +4788,7 @@
       <c r="D51" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E51" s="64">
+      <c r="E51" s="59">
         <v>477</v>
       </c>
       <c r="F51" s="22">
@@ -4771,7 +4804,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="52" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A52" s="22">
         <v>43252</v>
       </c>
@@ -4784,10 +4817,10 @@
       <c r="D52" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="64">
+      <c r="E52" s="59">
         <v>171</v>
       </c>
-      <c r="F52" s="64" t="s">
+      <c r="F52" s="59" t="s">
         <v>132</v>
       </c>
       <c r="G52" s="24" t="s">
@@ -4797,7 +4830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="53" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A53" s="22">
         <v>43042</v>
       </c>
@@ -4810,7 +4843,7 @@
       <c r="D53" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="64">
+      <c r="E53" s="59">
         <v>187</v>
       </c>
       <c r="F53" s="22">
@@ -4823,7 +4856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A54" s="22">
         <v>42986</v>
       </c>
@@ -4836,7 +4869,7 @@
       <c r="D54" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="64">
+      <c r="E54" s="59">
         <v>20</v>
       </c>
       <c r="F54" s="22">
@@ -4852,7 +4885,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A55" s="22">
         <v>42495</v>
       </c>
@@ -4865,7 +4898,7 @@
       <c r="D55" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="64">
+      <c r="E55" s="59">
         <v>154</v>
       </c>
       <c r="F55" s="22">
@@ -4878,7 +4911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A56" s="22">
         <v>42494</v>
       </c>
@@ -4891,10 +4924,10 @@
       <c r="D56" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E56" s="64">
+      <c r="E56" s="59">
         <v>60</v>
       </c>
-      <c r="F56" s="64" t="s">
+      <c r="F56" s="59" t="s">
         <v>139</v>
       </c>
       <c r="G56" s="24" t="s">
@@ -4904,7 +4937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A57" s="22">
         <v>42468</v>
       </c>
@@ -4917,7 +4950,7 @@
       <c r="D57" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="64">
+      <c r="E57" s="59">
         <v>131</v>
       </c>
       <c r="F57" s="22">
@@ -4930,7 +4963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A58" s="22">
         <v>42401</v>
       </c>
@@ -4943,10 +4976,10 @@
       <c r="D58" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E58" s="64">
+      <c r="E58" s="59">
         <v>241</v>
       </c>
-      <c r="F58" s="64" t="s">
+      <c r="F58" s="59" t="s">
         <v>142</v>
       </c>
       <c r="G58" s="24" t="s">
@@ -4956,7 +4989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="59" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A59" s="22">
         <v>42384</v>
       </c>
@@ -4969,10 +5002,10 @@
       <c r="D59" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="64" t="s">
+      <c r="E59" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="F59" s="64" t="s">
+      <c r="F59" s="59" t="s">
         <v>145</v>
       </c>
       <c r="G59" s="24" t="s">
@@ -4982,7 +5015,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A60" s="22">
         <v>42326</v>
       </c>
@@ -4995,7 +5028,7 @@
       <c r="D60" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E60" s="64">
+      <c r="E60" s="59">
         <v>70</v>
       </c>
       <c r="F60" s="22">
@@ -5008,7 +5041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="61" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A61" s="22">
         <v>42318</v>
       </c>
@@ -5021,7 +5054,7 @@
       <c r="D61" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="64" t="s">
+      <c r="E61" s="59" t="s">
         <v>148</v>
       </c>
       <c r="F61" s="22">
@@ -5037,7 +5070,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="62" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A62" s="22">
         <v>42178</v>
       </c>
@@ -5050,10 +5083,10 @@
       <c r="D62" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="F62" s="64" t="s">
+      <c r="F62" s="59" t="s">
         <v>151</v>
       </c>
       <c r="G62" s="24" t="s">
@@ -5063,7 +5096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A63" s="22">
         <v>42069</v>
       </c>
@@ -5076,7 +5109,7 @@
       <c r="D63" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="E63" s="64">
+      <c r="E63" s="59">
         <v>5</v>
       </c>
       <c r="F63" s="22">
@@ -5089,7 +5122,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="64" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A64" s="22">
         <v>42062</v>
       </c>
@@ -5102,7 +5135,7 @@
       <c r="D64" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E64" s="64">
+      <c r="E64" s="59">
         <v>142</v>
       </c>
       <c r="F64" s="22">
@@ -5115,7 +5148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A65" s="22">
         <v>41850</v>
       </c>
@@ -5128,7 +5161,7 @@
       <c r="D65" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="64">
+      <c r="E65" s="59">
         <v>115</v>
       </c>
       <c r="F65" s="22">
@@ -5144,7 +5177,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="66" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A66" s="22">
         <v>41820</v>
       </c>
@@ -5157,7 +5190,7 @@
       <c r="D66" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E66" s="64">
+      <c r="E66" s="59">
         <v>49</v>
       </c>
       <c r="F66" s="22">
@@ -5170,7 +5203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A67" s="22">
         <v>41724</v>
       </c>
@@ -5183,7 +5216,7 @@
       <c r="D67" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E67" s="64">
+      <c r="E67" s="59">
         <v>1</v>
       </c>
       <c r="F67" s="22">
@@ -5196,7 +5229,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A68" s="22">
         <v>41593</v>
       </c>
@@ -5209,7 +5242,7 @@
       <c r="D68" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="59">
         <v>66</v>
       </c>
       <c r="F68" s="22">
@@ -5222,7 +5255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A69" s="22">
         <v>41547</v>
       </c>
@@ -5235,7 +5268,7 @@
       <c r="D69" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="64">
+      <c r="E69" s="59">
         <v>3</v>
       </c>
       <c r="F69" s="22">
@@ -5248,7 +5281,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="70" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A70" s="22">
         <v>41495</v>
       </c>
@@ -5261,7 +5294,7 @@
       <c r="D70" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E70" s="64">
+      <c r="E70" s="59">
         <v>62</v>
       </c>
       <c r="F70" s="22">
@@ -5274,7 +5307,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="71" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A71" s="22">
         <v>41425</v>
       </c>
@@ -5287,7 +5320,7 @@
       <c r="D71" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="E71" s="64" t="s">
+      <c r="E71" s="59" t="s">
         <v>144</v>
       </c>
       <c r="F71" s="22">
@@ -5300,7 +5333,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A72" s="22">
         <v>41416</v>
       </c>
@@ -5313,7 +5346,7 @@
       <c r="D72" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E72" s="64">
+      <c r="E72" s="59">
         <v>51</v>
       </c>
       <c r="F72" s="22">
@@ -5326,7 +5359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="73" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A73" s="22">
         <v>41285</v>
       </c>
@@ -5339,7 +5372,7 @@
       <c r="D73" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E73" s="64">
+      <c r="E73" s="59">
         <v>150</v>
       </c>
       <c r="F73" s="22">
@@ -5355,7 +5388,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A74" s="22">
         <v>41087</v>
       </c>
@@ -5368,7 +5401,7 @@
       <c r="D74" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E74" s="64">
+      <c r="E74" s="59">
         <v>70</v>
       </c>
       <c r="F74" s="22">
@@ -5384,7 +5417,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A75" s="22">
         <v>41011</v>
       </c>
@@ -5397,7 +5430,7 @@
       <c r="D75" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="E75" s="64">
+      <c r="E75" s="59">
         <v>110</v>
       </c>
       <c r="F75" s="22">
@@ -5411,7 +5444,7 @@
       </c>
       <c r="I75" s="24"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A76" s="22">
         <v>40938</v>
       </c>
@@ -5424,7 +5457,7 @@
       <c r="D76" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E76" s="64">
+      <c r="E76" s="59">
         <v>16</v>
       </c>
       <c r="F76" s="22">
@@ -5438,7 +5471,7 @@
       </c>
       <c r="I76" s="24"/>
     </row>
-    <row r="77" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="77" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A77" s="22">
         <v>40833</v>
       </c>
@@ -5451,7 +5484,7 @@
       <c r="D77" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E77" s="64">
+      <c r="E77" s="59">
         <v>9</v>
       </c>
       <c r="F77" s="22">
@@ -5465,7 +5498,7 @@
       </c>
       <c r="I77" s="24"/>
     </row>
-    <row r="78" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="78" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A78" s="22">
         <v>40785</v>
       </c>
@@ -5478,10 +5511,10 @@
       <c r="D78" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E78" s="64">
+      <c r="E78" s="59">
         <v>98</v>
       </c>
-      <c r="F78" s="64" t="s">
+      <c r="F78" s="59" t="s">
         <v>173</v>
       </c>
       <c r="G78" s="24" t="s">
@@ -5492,7 +5525,7 @@
       </c>
       <c r="I78" s="24"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A79" s="22">
         <v>40752</v>
       </c>
@@ -5505,10 +5538,10 @@
       <c r="D79" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="E79" s="64">
+      <c r="E79" s="59">
         <v>21</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="59" t="s">
         <v>176</v>
       </c>
       <c r="G79" s="24" t="s">
@@ -5519,7 +5552,7 @@
       </c>
       <c r="I79" s="24"/>
     </row>
-    <row r="80" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="80" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A80" s="22">
         <v>40753</v>
       </c>
@@ -5532,10 +5565,10 @@
       <c r="D80" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E80" s="64">
+      <c r="E80" s="59">
         <v>98</v>
       </c>
-      <c r="F80" s="64" t="s">
+      <c r="F80" s="59" t="s">
         <v>178</v>
       </c>
       <c r="G80" s="24" t="s">
@@ -5546,7 +5579,7 @@
       </c>
       <c r="I80" s="24"/>
     </row>
-    <row r="81" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="81" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A81" s="22">
         <v>40688</v>
       </c>
@@ -5559,7 +5592,7 @@
       <c r="D81" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E81" s="64">
+      <c r="E81" s="59">
         <v>5</v>
       </c>
       <c r="F81" s="22">
@@ -5573,7 +5606,7 @@
       </c>
       <c r="I81" s="24"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A82" s="22">
         <v>40634</v>
       </c>
@@ -5586,7 +5619,7 @@
       <c r="D82" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E82" s="64">
+      <c r="E82" s="59">
         <v>122</v>
       </c>
       <c r="F82" s="22">
@@ -5600,7 +5633,7 @@
       </c>
       <c r="I82" s="24"/>
     </row>
-    <row r="83" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="83" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A83" s="22">
         <v>40589</v>
       </c>
@@ -5613,7 +5646,7 @@
       <c r="D83" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E83" s="64">
+      <c r="E83" s="59">
         <v>89</v>
       </c>
       <c r="F83" s="22">
@@ -5627,7 +5660,7 @@
       </c>
       <c r="I83" s="24"/>
     </row>
-    <row r="84" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="84" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A84" s="22">
         <v>40565</v>
       </c>
@@ -5640,10 +5673,10 @@
       <c r="D84" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E84" s="64">
+      <c r="E84" s="59">
         <v>26</v>
       </c>
-      <c r="F84" s="64" t="s">
+      <c r="F84" s="59" t="s">
         <v>183</v>
       </c>
       <c r="G84" s="24" t="s">
@@ -5654,7 +5687,7 @@
       </c>
       <c r="I84" s="24"/>
     </row>
-    <row r="85" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="85" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A85" s="22">
         <v>40410</v>
       </c>
@@ -5667,7 +5700,7 @@
       <c r="D85" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E85" s="64">
+      <c r="E85" s="59">
         <v>165</v>
       </c>
       <c r="F85" s="22">
@@ -5681,7 +5714,7 @@
       </c>
       <c r="I85" s="24"/>
     </row>
-    <row r="86" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="86" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A86" s="22">
         <v>40392</v>
       </c>
@@ -5694,7 +5727,7 @@
       <c r="D86" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="64">
+      <c r="E86" s="59">
         <v>8</v>
       </c>
       <c r="F86" s="22">
@@ -5708,7 +5741,7 @@
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A87" s="22">
         <v>40214</v>
       </c>
@@ -5721,10 +5754,10 @@
       <c r="D87" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E87" s="64">
+      <c r="E87" s="59">
         <v>66</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="59" t="s">
         <v>186</v>
       </c>
       <c r="G87" s="24" t="s">
@@ -5735,7 +5768,7 @@
       </c>
       <c r="I87" s="24"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A88" s="22">
         <v>40178</v>
       </c>
@@ -5748,10 +5781,10 @@
       <c r="D88" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E88" s="64">
+      <c r="E88" s="59">
         <v>103</v>
       </c>
-      <c r="F88" s="64" t="s">
+      <c r="F88" s="59" t="s">
         <v>188</v>
       </c>
       <c r="G88" s="24" t="s">
@@ -5764,7 +5797,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="89" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A89" s="22">
         <v>40137</v>
       </c>
@@ -5777,7 +5810,7 @@
       <c r="D89" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E89" s="64" t="s">
+      <c r="E89" s="59" t="s">
         <v>190</v>
       </c>
       <c r="F89" s="22">
@@ -5790,7 +5823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="90" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A90" s="22">
         <v>40137</v>
       </c>
@@ -5803,7 +5836,7 @@
       <c r="D90" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E90" s="64">
+      <c r="E90" s="59">
         <v>63</v>
       </c>
       <c r="F90" s="22">
@@ -5816,7 +5849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A91" s="22">
         <v>40094</v>
       </c>
@@ -5829,7 +5862,7 @@
       <c r="D91" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E91" s="64" t="s">
+      <c r="E91" s="59" t="s">
         <v>192</v>
       </c>
       <c r="F91" s="22">
@@ -5842,7 +5875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A92" s="22">
         <v>40091</v>
       </c>
@@ -5855,7 +5888,7 @@
       <c r="D92" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E92" s="64">
+      <c r="E92" s="59">
         <v>130</v>
       </c>
       <c r="F92" s="22">
@@ -5868,7 +5901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="93" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A93" s="22">
         <v>40046</v>
       </c>
@@ -5881,7 +5914,7 @@
       <c r="D93" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E93" s="64">
+      <c r="E93" s="59">
         <v>26</v>
       </c>
       <c r="F93" s="22">
@@ -5894,7 +5927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A94" s="22">
         <v>40007</v>
       </c>
@@ -5907,7 +5940,7 @@
       <c r="D94" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E94" s="64">
+      <c r="E94" s="59">
         <v>14</v>
       </c>
       <c r="F94" s="22">
@@ -5920,7 +5953,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="95" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A95" s="22">
         <v>40007</v>
       </c>
@@ -5933,7 +5966,7 @@
       <c r="D95" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="E95" s="64">
+      <c r="E95" s="59">
         <v>10</v>
       </c>
       <c r="F95" s="22">
@@ -5946,7 +5979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="14.25">
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="13.8">
       <c r="A96" s="22">
         <v>39995</v>
       </c>
@@ -5959,7 +5992,7 @@
       <c r="D96" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E96" s="64">
+      <c r="E96" s="59">
         <v>171</v>
       </c>
       <c r="F96" s="22">
@@ -5975,7 +6008,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="97" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="97" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A97" s="22">
         <v>39980</v>
       </c>
@@ -5988,7 +6021,7 @@
       <c r="D97" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="E97" s="64">
+      <c r="E97" s="59">
         <v>55</v>
       </c>
       <c r="F97" s="22">
@@ -6001,7 +6034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="98" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A98" s="22">
         <v>39931</v>
       </c>
@@ -6014,7 +6047,7 @@
       <c r="D98" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E98" s="64">
+      <c r="E98" s="59">
         <v>29</v>
       </c>
       <c r="F98" s="22">
@@ -6027,7 +6060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="99" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A99" s="22">
         <v>39918</v>
       </c>
@@ -6040,7 +6073,7 @@
       <c r="D99" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E99" s="64">
+      <c r="E99" s="59">
         <v>71</v>
       </c>
       <c r="F99" s="22">
@@ -6053,7 +6086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="100" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A100" s="22">
         <v>39883</v>
       </c>
@@ -6066,7 +6099,7 @@
       <c r="D100" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E100" s="64">
+      <c r="E100" s="59">
         <v>54</v>
       </c>
       <c r="F100" s="22">
@@ -6079,7 +6112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="101" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A101" s="22">
         <v>39881</v>
       </c>
@@ -6092,7 +6125,7 @@
       <c r="D101" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="64">
+      <c r="E101" s="59">
         <v>119</v>
       </c>
       <c r="F101" s="22">
@@ -6105,7 +6138,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="102" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A102" s="22">
         <v>39876</v>
       </c>
@@ -6118,7 +6151,7 @@
       <c r="D102" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="E102" s="64">
+      <c r="E102" s="59">
         <v>270</v>
       </c>
       <c r="F102" s="22">
@@ -6131,7 +6164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:14" s="5" customFormat="1" ht="14.25">
+    <row r="103" spans="1:14" s="5" customFormat="1" ht="13.8">
       <c r="A103" s="22">
         <v>39877</v>
       </c>
@@ -6144,7 +6177,7 @@
       <c r="D103" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E103" s="64">
+      <c r="E103" s="59">
         <v>121</v>
       </c>
       <c r="F103" s="22">
@@ -7324,15 +7357,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D7CA4A7758DDF4F8A78677D3B22BD47" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f32e13009e9660c0d5c2c5b7ed8445ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e19eab3b-0a92-46fc-9552-a493c76cdc00" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dceef0fefb3dead4f6c07070271e1f3" ns2:_="">
     <xsd:import namespace="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
@@ -7476,6 +7500,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -7483,13 +7516,43 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/ri/WARN Report.xlsx
+++ b/data/warn-scraper/cache/ri/WARN Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4B8664-6BC9-4631-BCD3-307DA1D16A59}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E43C28B4-3908-4176-A9E5-61C99C5CA500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="209">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -71,6 +71,27 @@
     <t>Union Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Conduent </t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>1 (Remote worker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideal US Talent Systems Worker OpCo LLC </t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Allied Group, LLC</t>
   </si>
   <si>
@@ -83,9 +104,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Northeast Transportation Services LLC</t>
   </si>
   <si>
@@ -648,15 +666,6 @@
   </si>
   <si>
     <t>East Providence and Providence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideal US Talent Systems Worker OpCo LLC </t>
-  </si>
-  <si>
-    <t>Minneapolis, MN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
   </si>
 </sst>
 </file>
@@ -987,9 +996,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1017,14 +1023,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1044,9 +1053,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1084,7 +1093,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1190,7 +1199,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1332,7 +1341,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1340,81 +1349,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="13.09765625" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" customWidth="1"/>
-    <col min="7" max="7" width="20.19921875" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
     <col min="9" max="9" width="51.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.2">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.15">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="48"/>
-      <c r="D3" s="71"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-    </row>
-    <row r="4" spans="1:19" s="54" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="78" t="s">
+      <c r="C4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="75" t="s">
         <v>9</v>
       </c>
       <c r="J4"/>
@@ -1428,129 +1437,150 @@
       <c r="R4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="1:19" ht="31.2">
-      <c r="A5" s="72">
+    <row r="5" spans="1:19" ht="16.5">
+      <c r="A5" s="71">
+        <v>46199</v>
+      </c>
+      <c r="B5" s="71">
+        <v>46202</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="71">
+        <v>46262</v>
+      </c>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="1:19" ht="31.15">
+      <c r="A6" s="71">
         <v>46143</v>
       </c>
-      <c r="B5" s="72">
+      <c r="B6" s="71">
         <v>46147</v>
       </c>
-      <c r="C5" s="82" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>205</v>
-      </c>
-      <c r="F5" s="72">
+      <c r="C6" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="71">
         <v>46204</v>
       </c>
-      <c r="H5" s="80" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" s="54" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A6" s="72">
+      <c r="H6" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="54" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A7" s="71">
         <v>46107</v>
       </c>
-      <c r="B6" s="72">
+      <c r="B7" s="71">
         <v>46112</v>
       </c>
-      <c r="C6" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="80">
+      <c r="C7" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="79">
         <v>154</v>
       </c>
-      <c r="F6" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="73"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="74"/>
-    </row>
-    <row r="7" spans="1:19" s="75" customFormat="1" ht="31.2">
-      <c r="A7" s="72">
+      <c r="F7" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="72"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
+    </row>
+    <row r="8" spans="1:19" s="74" customFormat="1" ht="31.15">
+      <c r="A8" s="71">
         <v>46100</v>
       </c>
-      <c r="B7" s="72">
+      <c r="B8" s="71">
         <v>46100</v>
       </c>
-      <c r="C7" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="80">
+      <c r="C8" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="79">
         <v>52</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F8" s="71">
         <v>46151</v>
       </c>
-      <c r="G7" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="74"/>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="70">
+      <c r="G8" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="70">
         <v>46035</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B9" s="70">
         <v>46035</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="28">
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="28">
         <v>38</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F9" s="70">
         <v>46096</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>14</v>
+      <c r="G9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1572,50 +1602,50 @@
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19.95" customHeight="1">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-    </row>
-    <row r="2" spans="1:19" ht="19.95" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-    </row>
-    <row r="3" spans="1:19" ht="19.95" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+    </row>
+    <row r="2" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="48"/>
-      <c r="D3" s="71"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-    </row>
-    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.95" customHeight="1">
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
@@ -1662,10 +1692,10 @@
         <v>45910</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5" s="62">
         <v>2</v>
@@ -1674,10 +1704,10 @@
         <v>45975</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="63"/>
       <c r="J5"/>
@@ -1699,10 +1729,10 @@
         <v>45903</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E6" s="62">
         <v>105</v>
@@ -1711,13 +1741,13 @@
         <v>45964</v>
       </c>
       <c r="G6" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="61" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -1730,7 +1760,7 @@
       <c r="R6"/>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" s="54" customFormat="1" ht="31.2">
+    <row r="7" spans="1:19" s="54" customFormat="1" ht="31.15">
       <c r="A7" s="63">
         <v>45814</v>
       </c>
@@ -1738,10 +1768,10 @@
         <v>45816</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" s="62">
         <v>125</v>
@@ -1750,10 +1780,10 @@
         <v>45874</v>
       </c>
       <c r="G7" s="62" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1775,10 +1805,10 @@
         <v>45736</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E8" s="62">
         <v>20</v>
@@ -1787,10 +1817,10 @@
         <v>45800</v>
       </c>
       <c r="G8" s="61" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1812,20 +1842,20 @@
         <v>45694</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63">
         <v>45815</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1853,55 +1883,55 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S123"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.3984375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="28.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.59765625" customWidth="1"/>
+    <col min="9" max="9" width="71.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-    </row>
-    <row r="3" spans="1:19" ht="31.2">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:19" ht="31.15">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
       <c r="C3" s="48"/>
-      <c r="D3" s="71"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="25"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-    </row>
-    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.95" customHeight="1">
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+    </row>
+    <row r="4" spans="1:19" s="54" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A4" s="65" t="s">
         <v>1</v>
       </c>
@@ -1948,10 +1978,10 @@
         <v>45621</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="38">
         <v>796</v>
@@ -1960,10 +1990,10 @@
         <v>45682</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="38"/>
     </row>
@@ -1975,10 +2005,10 @@
         <v>45617</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6" s="38">
         <v>121</v>
@@ -1987,10 +2017,10 @@
         <v>45681</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="34"/>
@@ -2012,10 +2042,10 @@
         <v>45608</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" s="38">
         <v>136</v>
@@ -2024,13 +2054,13 @@
         <v>45726</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
@@ -2051,22 +2081,22 @@
         <v>45572</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E8" s="38">
         <v>632</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
@@ -2088,10 +2118,10 @@
         <v>45567</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="38">
         <v>1</v>
@@ -2100,7 +2130,7 @@
         <v>45626</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
@@ -2113,20 +2143,20 @@
         <v>45560</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E10" s="38">
         <v>13</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" s="38"/>
     </row>
@@ -2138,20 +2168,20 @@
         <v>45526</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E11" s="38">
         <v>117</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" s="38"/>
     </row>
@@ -2163,10 +2193,10 @@
         <v>45504</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E12" s="38">
         <v>205</v>
@@ -2175,10 +2205,10 @@
         <v>45658</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="38"/>
     </row>
@@ -2190,10 +2220,10 @@
         <v>45485</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E13" s="38">
         <v>58</v>
@@ -2202,10 +2232,10 @@
         <v>45541</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="38"/>
     </row>
@@ -2217,10 +2247,10 @@
         <v>45432</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14" s="38">
         <v>30</v>
@@ -2229,27 +2259,27 @@
         <v>45488</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B15" s="40">
         <v>45421</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E15" s="38">
         <v>1029</v>
@@ -2258,13 +2288,13 @@
         <v>45473</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2275,22 +2305,22 @@
         <v>45414</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E16" s="38">
         <v>36</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" s="38"/>
     </row>
@@ -2302,22 +2332,22 @@
         <v>45383</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F17" s="40">
         <v>45412</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I17" s="38"/>
     </row>
@@ -2329,10 +2359,10 @@
         <v>45383</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E18" s="38">
         <v>1</v>
@@ -2341,10 +2371,10 @@
         <v>45443</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" s="38"/>
     </row>
@@ -2356,10 +2386,10 @@
         <v>45349</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E19" s="38">
         <v>48</v>
@@ -2368,10 +2398,10 @@
         <v>45611</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I19" s="38"/>
     </row>
@@ -2383,10 +2413,10 @@
         <v>45328</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E20" s="38">
         <v>130</v>
@@ -2395,13 +2425,13 @@
         <v>45384</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2412,10 +2442,10 @@
         <v>45316</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E21" s="38">
         <v>1</v>
@@ -2424,10 +2454,10 @@
         <v>45316</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" s="40"/>
     </row>
@@ -3464,53 +3494,53 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="103.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="103.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-    </row>
-    <row r="3" spans="1:9" ht="31.2">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:9" ht="31.15">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1">
       <c r="A4" s="35" t="s">
@@ -3520,7 +3550,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>4</v>
@@ -3541,7 +3571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A5" s="55">
         <v>45191</v>
       </c>
@@ -3549,10 +3579,10 @@
         <v>45191</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E5" s="6">
         <v>136</v>
@@ -3561,14 +3591,14 @@
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A6" s="55">
         <v>45156</v>
       </c>
@@ -3576,26 +3606,26 @@
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A7" s="55">
         <v>45191</v>
       </c>
@@ -3603,10 +3633,10 @@
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E7" s="38">
         <v>52</v>
@@ -3615,13 +3645,13 @@
         <v>45153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A8" s="55">
         <v>45156</v>
       </c>
@@ -3629,10 +3659,10 @@
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6">
         <v>211</v>
@@ -3641,16 +3671,16 @@
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A9" s="40">
         <v>45153</v>
       </c>
@@ -3658,10 +3688,10 @@
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E9" s="6">
         <v>249</v>
@@ -3670,16 +3700,16 @@
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A10" s="55">
         <v>45112</v>
       </c>
@@ -3687,10 +3717,10 @@
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E10" s="6">
         <v>169</v>
@@ -3699,16 +3729,16 @@
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A11" s="55">
         <v>45107</v>
       </c>
@@ -3716,10 +3746,10 @@
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E11" s="6">
         <v>75</v>
@@ -3728,16 +3758,16 @@
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A12" s="55">
         <v>45063</v>
       </c>
@@ -3745,10 +3775,10 @@
         <v>44937</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E12" s="38">
         <v>81</v>
@@ -3757,14 +3787,14 @@
         <v>44990</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A13" s="57">
         <v>44949</v>
       </c>
@@ -3772,10 +3802,10 @@
         <v>44831</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E13" s="58">
         <v>1</v>
@@ -3784,14 +3814,14 @@
         <v>44890</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A14" s="40">
         <v>44930</v>
       </c>
@@ -3799,10 +3829,10 @@
         <v>44817</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>80</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>74</v>
       </c>
       <c r="E14" s="58">
         <v>77</v>
@@ -3811,14 +3841,14 @@
         <v>44880</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A15" s="22">
         <v>44827</v>
       </c>
@@ -3826,10 +3856,10 @@
         <v>44594</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E15" s="59">
         <v>198</v>
@@ -3838,13 +3868,13 @@
         <v>44659</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A16" s="22">
         <v>44817</v>
       </c>
@@ -3852,10 +3882,10 @@
         <v>44336</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E16" s="59">
         <v>94</v>
@@ -3864,16 +3894,16 @@
         <v>44394</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A17" s="22">
         <v>44595</v>
       </c>
@@ -3881,10 +3911,10 @@
         <v>44342</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E17" s="59">
         <v>464</v>
@@ -3893,13 +3923,13 @@
         <v>44403</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A18" s="22">
         <v>44334</v>
       </c>
@@ -3907,10 +3937,10 @@
         <v>44104</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E18" s="59">
         <v>13</v>
@@ -3919,13 +3949,13 @@
         <v>44104</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A19" s="22">
         <v>44342</v>
       </c>
@@ -3933,10 +3963,10 @@
         <v>44068</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E19" s="59">
         <v>40</v>
@@ -3945,13 +3975,13 @@
         <v>44061</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A20" s="22">
         <v>44105</v>
       </c>
@@ -3959,10 +3989,10 @@
         <v>44060</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E20" s="59">
         <v>106</v>
@@ -3971,13 +4001,13 @@
         <v>44057</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A21" s="22">
         <v>44064</v>
       </c>
@@ -3985,10 +4015,10 @@
         <v>44056</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E21" s="59">
         <v>272</v>
@@ -3997,16 +4027,16 @@
         <v>43914</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A22" s="22">
         <v>44057</v>
       </c>
@@ -4014,10 +4044,10 @@
         <v>44040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E22" s="59">
         <v>1043</v>
@@ -4026,16 +4056,16 @@
         <v>44104</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A23" s="22">
         <v>44049</v>
       </c>
@@ -4043,10 +4073,10 @@
         <v>44040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E23" s="59">
         <v>296</v>
@@ -4055,16 +4085,16 @@
         <v>44104</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A24" s="22">
         <v>44054</v>
       </c>
@@ -4072,10 +4102,10 @@
         <v>44042</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E24" s="59">
         <v>73</v>
@@ -4084,13 +4114,13 @@
         <v>44075</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A25" s="22">
         <v>44054</v>
       </c>
@@ -4098,10 +4128,10 @@
         <v>44022</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E25" s="59">
         <v>127</v>
@@ -4110,16 +4140,16 @@
         <v>44044</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A26" s="22">
         <v>44046</v>
       </c>
@@ -4127,10 +4157,10 @@
         <v>44004</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E26" s="59">
         <v>71</v>
@@ -4139,13 +4169,13 @@
         <v>43973</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A27" s="22">
         <v>44027</v>
       </c>
@@ -4153,10 +4183,10 @@
         <v>44012</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E27" s="59">
         <v>65</v>
@@ -4165,13 +4195,13 @@
         <v>44012</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A28" s="22">
         <v>44004</v>
       </c>
@@ -4179,10 +4209,10 @@
         <v>43985</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E28" s="59">
         <v>65</v>
@@ -4191,13 +4221,13 @@
         <v>43904</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A29" s="22">
         <v>44012</v>
       </c>
@@ -4205,10 +4235,10 @@
         <v>43980</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E29" s="59">
         <v>231</v>
@@ -4217,13 +4247,13 @@
         <v>43980</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A30" s="22">
         <v>43985</v>
       </c>
@@ -4231,10 +4261,10 @@
         <v>44068</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E30" s="59">
         <v>72</v>
@@ -4243,13 +4273,13 @@
         <v>43958</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A31" s="22">
         <v>43980</v>
       </c>
@@ -4257,10 +4287,10 @@
         <v>43948</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E31" s="59">
         <v>136</v>
@@ -4269,13 +4299,13 @@
         <v>43906</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A32" s="40">
         <v>44063</v>
       </c>
@@ -4283,10 +4313,10 @@
         <v>43942</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E32" s="59">
         <v>5</v>
@@ -4295,13 +4325,13 @@
         <v>43942</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A33" s="40">
         <v>43948</v>
       </c>
@@ -4309,10 +4339,10 @@
         <v>43944</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E33" s="59">
         <v>1</v>
@@ -4321,13 +4351,13 @@
         <v>43941</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A34" s="40">
         <v>43942</v>
       </c>
@@ -4335,10 +4365,10 @@
         <v>43938</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E34" s="59">
         <v>13</v>
@@ -4347,13 +4377,13 @@
         <v>43938</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A35" s="22">
         <v>43941</v>
       </c>
@@ -4361,10 +4391,10 @@
         <v>43935</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E35" s="59">
         <v>51</v>
@@ -4373,13 +4403,13 @@
         <v>43906</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A36" s="22">
         <v>43907</v>
       </c>
@@ -4387,10 +4417,10 @@
         <v>43925</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E36" s="59">
         <v>110</v>
@@ -4399,13 +4429,13 @@
         <v>43927</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A37" s="22">
         <v>43927</v>
       </c>
@@ -4413,10 +4443,10 @@
         <v>43917</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E37" s="59">
         <v>37</v>
@@ -4425,13 +4455,13 @@
         <v>43916</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A38" s="22">
         <v>43925</v>
       </c>
@@ -4439,10 +4469,10 @@
         <v>43913</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E38" s="59">
         <v>146</v>
@@ -4451,16 +4481,16 @@
         <v>43898</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A39" s="22">
         <v>43916</v>
       </c>
@@ -4468,10 +4498,10 @@
         <v>43910</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E39" s="59">
         <v>87</v>
@@ -4480,13 +4510,13 @@
         <v>43910</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A40" s="22">
         <v>43916</v>
       </c>
@@ -4494,10 +4524,10 @@
         <v>43913</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E40" s="59">
         <v>110</v>
@@ -4506,13 +4536,13 @@
         <v>43906</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A41" s="22">
         <v>43910</v>
       </c>
@@ -4520,10 +4550,10 @@
         <v>43510</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E41" s="59">
         <v>1</v>
@@ -4532,13 +4562,13 @@
         <v>43567</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A42" s="22">
         <v>43909</v>
       </c>
@@ -4546,25 +4576,25 @@
         <v>43486</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E42" s="59">
         <v>59</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A43" s="22">
         <v>43509</v>
       </c>
@@ -4572,10 +4602,10 @@
         <v>43479</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E43" s="59">
         <v>62</v>
@@ -4584,13 +4614,13 @@
         <v>43542</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A44" s="22">
         <v>43486</v>
       </c>
@@ -4598,10 +4628,10 @@
         <v>43413</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E44" s="59">
         <v>51</v>
@@ -4610,13 +4640,13 @@
         <v>43131</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A45" s="22">
         <v>43479</v>
       </c>
@@ -4624,10 +4654,10 @@
         <v>43405</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E45" s="59">
         <v>92</v>
@@ -4636,13 +4666,13 @@
         <v>43465</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A46" s="22">
         <v>43405</v>
       </c>
@@ -4650,10 +4680,10 @@
         <v>43405</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E46" s="59">
         <v>181</v>
@@ -4662,13 +4692,13 @@
         <v>43469</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A47" s="22">
         <v>76277</v>
       </c>
@@ -4676,10 +4706,10 @@
         <v>43382</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E47" s="59">
         <v>180</v>
@@ -4688,13 +4718,13 @@
         <v>43382</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A48" s="22">
         <v>76268</v>
       </c>
@@ -4702,10 +4732,10 @@
         <v>43363</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E48" s="59">
         <v>83</v>
@@ -4714,13 +4744,13 @@
         <v>43434</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A49" s="22">
         <v>43382</v>
       </c>
@@ -4728,10 +4758,10 @@
         <v>43276</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E49" s="59">
         <v>64</v>
@@ -4740,16 +4770,16 @@
         <v>43339</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A50" s="22">
         <v>43362</v>
       </c>
@@ -4757,10 +4787,10 @@
         <v>43252</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E50" s="59">
         <v>149</v>
@@ -4769,13 +4799,13 @@
         <v>43312</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A51" s="22">
         <v>43273</v>
       </c>
@@ -4783,10 +4813,10 @@
         <v>43042</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E51" s="59">
         <v>477</v>
@@ -4795,16 +4825,16 @@
         <v>43112</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A52" s="22">
         <v>43252</v>
       </c>
@@ -4812,25 +4842,25 @@
         <v>42990</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E52" s="59">
         <v>171</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A53" s="22">
         <v>43042</v>
       </c>
@@ -4838,10 +4868,10 @@
         <v>42496</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E53" s="59">
         <v>187</v>
@@ -4850,13 +4880,13 @@
         <v>42492</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A54" s="22">
         <v>42986</v>
       </c>
@@ -4864,10 +4894,10 @@
         <v>42495</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E54" s="59">
         <v>20</v>
@@ -4876,16 +4906,16 @@
         <v>42551</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A55" s="22">
         <v>42495</v>
       </c>
@@ -4893,10 +4923,10 @@
         <v>42468</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E55" s="59">
         <v>154</v>
@@ -4905,13 +4935,13 @@
         <v>42528</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A56" s="22">
         <v>42494</v>
       </c>
@@ -4919,25 +4949,25 @@
         <v>42401</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E56" s="59">
         <v>60</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A57" s="22">
         <v>42468</v>
       </c>
@@ -4945,10 +4975,10 @@
         <v>42384</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E57" s="59">
         <v>131</v>
@@ -4957,13 +4987,13 @@
         <v>42405</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A58" s="22">
         <v>42401</v>
       </c>
@@ -4971,25 +5001,25 @@
         <v>42326</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E58" s="59">
         <v>241</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A59" s="22">
         <v>42384</v>
       </c>
@@ -4997,25 +5027,25 @@
         <v>42320</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F59" s="59" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A60" s="22">
         <v>42326</v>
       </c>
@@ -5023,10 +5053,10 @@
         <v>42180</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E60" s="59">
         <v>70</v>
@@ -5035,13 +5065,13 @@
         <v>42240</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A61" s="22">
         <v>42318</v>
       </c>
@@ -5049,28 +5079,28 @@
         <v>42074</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E61" s="59" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F61" s="22">
         <v>42141</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A62" s="22">
         <v>42178</v>
       </c>
@@ -5078,25 +5108,25 @@
         <v>42065</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A63" s="22">
         <v>42069</v>
       </c>
@@ -5104,10 +5134,10 @@
         <v>41850</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E63" s="59">
         <v>5</v>
@@ -5116,13 +5146,13 @@
         <v>41912</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A64" s="22">
         <v>42062</v>
       </c>
@@ -5130,10 +5160,10 @@
         <v>41821</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E64" s="59">
         <v>142</v>
@@ -5142,13 +5172,13 @@
         <v>41882</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A65" s="22">
         <v>41850</v>
       </c>
@@ -5156,10 +5186,10 @@
         <v>41729</v>
       </c>
       <c r="C65" s="24" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E65" s="59">
         <v>115</v>
@@ -5168,16 +5198,16 @@
         <v>41774</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A66" s="22">
         <v>41820</v>
       </c>
@@ -5185,10 +5215,10 @@
         <v>41596</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E66" s="59">
         <v>49</v>
@@ -5197,13 +5227,13 @@
         <v>41654</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A67" s="22">
         <v>41724</v>
       </c>
@@ -5211,10 +5241,10 @@
         <v>41547</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E67" s="59">
         <v>1</v>
@@ -5223,13 +5253,13 @@
         <v>41608</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A68" s="22">
         <v>41593</v>
       </c>
@@ -5237,10 +5267,10 @@
         <v>41502</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E68" s="59">
         <v>66</v>
@@ -5249,13 +5279,13 @@
         <v>41555</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A69" s="22">
         <v>41547</v>
       </c>
@@ -5263,10 +5293,10 @@
         <v>41438</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E69" s="59">
         <v>3</v>
@@ -5275,13 +5305,13 @@
         <v>41425</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A70" s="22">
         <v>41495</v>
       </c>
@@ -5289,10 +5319,10 @@
         <v>41417</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E70" s="59">
         <v>62</v>
@@ -5301,13 +5331,13 @@
         <v>41485</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A71" s="22">
         <v>41425</v>
       </c>
@@ -5315,25 +5345,25 @@
         <v>41285</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F71" s="22">
         <v>41347</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A72" s="22">
         <v>41416</v>
       </c>
@@ -5341,10 +5371,10 @@
         <v>41087</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E72" s="59">
         <v>51</v>
@@ -5353,13 +5383,13 @@
         <v>41148</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A73" s="22">
         <v>41285</v>
       </c>
@@ -5367,10 +5397,10 @@
         <v>41011</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E73" s="59">
         <v>150</v>
@@ -5379,16 +5409,16 @@
         <v>41071</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A74" s="22">
         <v>41087</v>
       </c>
@@ -5396,10 +5426,10 @@
         <v>40939</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E74" s="59">
         <v>70</v>
@@ -5408,16 +5438,16 @@
         <v>41000</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A75" s="22">
         <v>41011</v>
       </c>
@@ -5425,10 +5455,10 @@
         <v>40833</v>
       </c>
       <c r="C75" s="24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E75" s="59">
         <v>110</v>
@@ -5437,14 +5467,14 @@
         <v>40833</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I75" s="24"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A76" s="22">
         <v>40938</v>
       </c>
@@ -5452,10 +5482,10 @@
         <v>40788</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E76" s="59">
         <v>16</v>
@@ -5464,14 +5494,14 @@
         <v>40846</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I76" s="24"/>
     </row>
-    <row r="77" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="77" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A77" s="22">
         <v>40833</v>
       </c>
@@ -5479,10 +5509,10 @@
         <v>40758</v>
       </c>
       <c r="C77" s="24" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E77" s="59">
         <v>9</v>
@@ -5491,14 +5521,14 @@
         <v>40816</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I77" s="24"/>
     </row>
-    <row r="78" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="78" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A78" s="22">
         <v>40785</v>
       </c>
@@ -5506,26 +5536,26 @@
         <v>40756</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E78" s="59">
         <v>98</v>
       </c>
       <c r="F78" s="59" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" s="24"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A79" s="22">
         <v>40752</v>
       </c>
@@ -5533,26 +5563,26 @@
         <v>40690</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E79" s="59">
         <v>21</v>
       </c>
       <c r="F79" s="59" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I79" s="24"/>
     </row>
-    <row r="80" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="80" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A80" s="22">
         <v>40753</v>
       </c>
@@ -5560,26 +5590,26 @@
         <v>40634</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E80" s="59">
         <v>98</v>
       </c>
       <c r="F80" s="59" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I80" s="24"/>
     </row>
-    <row r="81" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="81" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A81" s="22">
         <v>40688</v>
       </c>
@@ -5587,10 +5617,10 @@
         <v>40589</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E81" s="59">
         <v>5</v>
@@ -5599,14 +5629,14 @@
         <v>40644</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I81" s="24"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A82" s="22">
         <v>40634</v>
       </c>
@@ -5614,10 +5644,10 @@
         <v>40568</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E82" s="59">
         <v>122</v>
@@ -5626,14 +5656,14 @@
         <v>40592</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I82" s="24"/>
     </row>
-    <row r="83" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="83" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A83" s="22">
         <v>40589</v>
       </c>
@@ -5641,10 +5671,10 @@
         <v>40413</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E83" s="59">
         <v>89</v>
@@ -5653,14 +5683,14 @@
         <v>40452</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I83" s="24"/>
     </row>
-    <row r="84" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="84" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A84" s="22">
         <v>40565</v>
       </c>
@@ -5668,26 +5698,26 @@
         <v>40217</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D84" s="24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E84" s="59">
         <v>26</v>
       </c>
       <c r="F84" s="59" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I84" s="24"/>
     </row>
-    <row r="85" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="85" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A85" s="22">
         <v>40410</v>
       </c>
@@ -5695,10 +5725,10 @@
         <v>40217</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E85" s="59">
         <v>165</v>
@@ -5707,14 +5737,14 @@
         <v>40217</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I85" s="24"/>
     </row>
-    <row r="86" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="86" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A86" s="22">
         <v>40392</v>
       </c>
@@ -5722,10 +5752,10 @@
         <v>40182</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E86" s="59">
         <v>8</v>
@@ -5734,14 +5764,14 @@
         <v>40210</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A87" s="22">
         <v>40214</v>
       </c>
@@ -5749,26 +5779,26 @@
         <v>40141</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E87" s="59">
         <v>66</v>
       </c>
       <c r="F87" s="59" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I87" s="24"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.8">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A88" s="22">
         <v>40178</v>
       </c>
@@ -5776,28 +5806,28 @@
         <v>40141</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E88" s="59">
         <v>103</v>
       </c>
       <c r="F88" s="59" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A89" s="22">
         <v>40137</v>
       </c>
@@ -5805,25 +5835,25 @@
         <v>40094</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F89" s="22">
         <v>40147</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A90" s="22">
         <v>40137</v>
       </c>
@@ -5831,10 +5861,10 @@
         <v>40091</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E90" s="59">
         <v>63</v>
@@ -5843,13 +5873,13 @@
         <v>40148</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A91" s="22">
         <v>40094</v>
       </c>
@@ -5857,25 +5887,25 @@
         <v>40050</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E91" s="59" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F91" s="22">
         <v>39895</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A92" s="22">
         <v>40091</v>
       </c>
@@ -5883,10 +5913,10 @@
         <v>40008</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E92" s="59">
         <v>130</v>
@@ -5895,13 +5925,13 @@
         <v>39895</v>
       </c>
       <c r="G92" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A93" s="22">
         <v>40046</v>
       </c>
@@ -5909,10 +5939,10 @@
         <v>40008</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E93" s="59">
         <v>26</v>
@@ -5921,13 +5951,13 @@
         <v>40001</v>
       </c>
       <c r="G93" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A94" s="22">
         <v>40007</v>
       </c>
@@ -5935,10 +5965,10 @@
         <v>39895</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E94" s="59">
         <v>14</v>
@@ -5947,13 +5977,13 @@
         <v>39895</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A95" s="22">
         <v>40007</v>
       </c>
@@ -5961,10 +5991,10 @@
         <v>39996</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E95" s="59">
         <v>10</v>
@@ -5973,13 +6003,13 @@
         <v>40041</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="13.9">
       <c r="A96" s="22">
         <v>39995</v>
       </c>
@@ -5987,10 +6017,10 @@
         <v>39932</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E96" s="59">
         <v>171</v>
@@ -5999,16 +6029,16 @@
         <v>39994</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A97" s="22">
         <v>39980</v>
       </c>
@@ -6016,10 +6046,10 @@
         <v>39918</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E97" s="59">
         <v>55</v>
@@ -6028,13 +6058,13 @@
         <v>39994</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A98" s="22">
         <v>39931</v>
       </c>
@@ -6042,10 +6072,10 @@
         <v>39882</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E98" s="59">
         <v>29</v>
@@ -6054,13 +6084,13 @@
         <v>39943</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A99" s="22">
         <v>39918</v>
       </c>
@@ -6068,10 +6098,10 @@
         <v>39881</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E99" s="59">
         <v>71</v>
@@ -6080,13 +6110,13 @@
         <v>39941</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A100" s="22">
         <v>39883</v>
       </c>
@@ -6094,10 +6124,10 @@
         <v>39878</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D100" s="24" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E100" s="59">
         <v>54</v>
@@ -6106,13 +6136,13 @@
         <v>39935</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A101" s="22">
         <v>39881</v>
       </c>
@@ -6120,10 +6150,10 @@
         <v>39877</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D101" s="24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E101" s="59">
         <v>119</v>
@@ -6132,13 +6162,13 @@
         <v>39943</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A102" s="22">
         <v>39876</v>
       </c>
@@ -6146,10 +6176,10 @@
         <v>39864</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D102" s="24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E102" s="59">
         <v>270</v>
@@ -6158,13 +6188,13 @@
         <v>39828</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" s="5" customFormat="1" ht="13.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="5" customFormat="1" ht="13.9">
       <c r="A103" s="22">
         <v>39877</v>
       </c>
@@ -6172,10 +6202,10 @@
         <v>39825</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D103" s="24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E103" s="59">
         <v>121</v>
@@ -6184,10 +6214,10 @@
         <v>39821</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -7357,6 +7387,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D7CA4A7758DDF4F8A78677D3B22BD47" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f32e13009e9660c0d5c2c5b7ed8445ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e19eab3b-0a92-46fc-9552-a493c76cdc00" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dceef0fefb3dead4f6c07070271e1f3" ns2:_="">
     <xsd:import namespace="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
@@ -7500,59 +7545,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}"/>
 </file>